--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,6 +891,3686 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127838069</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>572084</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7078450</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127836515</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>571804</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7078630</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127836856</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>571858</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7078617</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127835362</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>571922</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7078336</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127838430</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78779</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>572136</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7078357</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127837929</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>572076</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7078468</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127836491</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>571822</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7078604</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127837975</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>572082</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7078455</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127836170</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>571920</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7078374</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127837620</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>572003</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7078559</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127837171</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78779</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>571911</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7078553</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127839625</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>572022</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7078301</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127837382</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>571975</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7078587</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127839595</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78779</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>572030</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7078309</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127837562</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>571988</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7078571</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127836801</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>571857</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7078617</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127835846</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>571950</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7078282</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127836645</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>571821</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7078612</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127837292</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>571959</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7078569</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127838341</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>572114</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7078380</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127837312</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>571968</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7078566</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127839604</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>572030</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7078309</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127835378</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>571927</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7078333</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127836444</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78779</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>571831</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7078599</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127837626</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78778</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>571995</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7078559</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127837089</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>571919</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7078558</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127838414</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>572136</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7078357</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127837719</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>572033</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7078531</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127839665</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>572000</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7078322</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127837544</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>571972</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7078577</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127837406</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>571965</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7078578</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127836771</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92628</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>571861</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7078614</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127837781</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>572047</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7078503</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>127838069</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,45 +1010,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127836515</v>
+        <v>127835362</v>
       </c>
       <c r="B5" t="n">
-        <v>92628</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571804</v>
+        <v>571922</v>
       </c>
       <c r="R5" t="n">
-        <v>7078630</v>
+        <v>7078336</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1095,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,22 +1115,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127836856</v>
+        <v>127836515</v>
       </c>
       <c r="B6" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571858</v>
+        <v>571804</v>
       </c>
       <c r="R6" t="n">
-        <v>7078617</v>
+        <v>7078630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1197,7 +1207,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,50 +1234,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127835362</v>
+        <v>127836856</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>92631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571922</v>
+        <v>571858</v>
       </c>
       <c r="R7" t="n">
-        <v>7078336</v>
+        <v>7078617</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,12 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,12 +1329,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1344,7 +1344,7 @@
         <v>127838430</v>
       </c>
       <c r="B8" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>127837929</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>127836491</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>127837975</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,45 +1789,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127836170</v>
+        <v>127837171</v>
       </c>
       <c r="B12" t="n">
-        <v>92628</v>
+        <v>78782</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571920</v>
+        <v>571911</v>
       </c>
       <c r="R12" t="n">
-        <v>7078374</v>
+        <v>7078553</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,45 +1896,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127837620</v>
+        <v>127836170</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>92631</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572003</v>
+        <v>571920</v>
       </c>
       <c r="R13" t="n">
-        <v>7078559</v>
+        <v>7078374</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,10 +2003,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127837171</v>
+        <v>127837620</v>
       </c>
       <c r="B14" t="n">
-        <v>78779</v>
+        <v>79023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,21 +2014,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571911</v>
+        <v>572003</v>
       </c>
       <c r="R14" t="n">
-        <v>7078553</v>
+        <v>7078559</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,50 +2110,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127839625</v>
+        <v>127837382</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>92631</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572022</v>
+        <v>571975</v>
       </c>
       <c r="R15" t="n">
-        <v>7078301</v>
+        <v>7078587</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,7 +2180,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2195,12 +2190,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2227,45 +2217,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127837382</v>
+        <v>127839625</v>
       </c>
       <c r="B16" t="n">
-        <v>92628</v>
+        <v>57666</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571975</v>
+        <v>572022</v>
       </c>
       <c r="R16" t="n">
-        <v>7078587</v>
+        <v>7078301</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,7 +2292,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2307,7 +2302,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,7 +2337,7 @@
         <v>127839595</v>
       </c>
       <c r="B17" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>127837562</v>
       </c>
       <c r="B18" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>127836801</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>127835846</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>127836645</v>
       </c>
       <c r="B21" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>127837292</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>127838341</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>127837312</v>
       </c>
       <c r="B24" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>127839604</v>
       </c>
       <c r="B25" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>127835378</v>
       </c>
       <c r="B26" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>127836444</v>
       </c>
       <c r="B27" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>127837626</v>
       </c>
       <c r="B28" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>127837089</v>
       </c>
       <c r="B29" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>127838414</v>
       </c>
       <c r="B30" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>127837719</v>
       </c>
       <c r="B31" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4019,45 +4019,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127839665</v>
+        <v>127837544</v>
       </c>
       <c r="B32" t="n">
-        <v>92628</v>
+        <v>79023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572000</v>
+        <v>571972</v>
       </c>
       <c r="R32" t="n">
-        <v>7078322</v>
+        <v>7078577</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4114,57 +4114,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127837544</v>
+        <v>127839665</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>92631</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571972</v>
+        <v>572000</v>
       </c>
       <c r="R33" t="n">
-        <v>7078577</v>
+        <v>7078322</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4221,12 +4221,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4236,7 +4236,7 @@
         <v>127837406</v>
       </c>
       <c r="B34" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>127836771</v>
       </c>
       <c r="B35" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>127837781</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>127838069</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,50 +1010,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127835362</v>
+        <v>127836515</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>92639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571922</v>
+        <v>571804</v>
       </c>
       <c r="R5" t="n">
-        <v>7078336</v>
+        <v>7078630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,12 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,22 +1105,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127836515</v>
+        <v>127836856</v>
       </c>
       <c r="B6" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1162,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571804</v>
+        <v>571858</v>
       </c>
       <c r="R6" t="n">
-        <v>7078630</v>
+        <v>7078617</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1187,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,7 +1197,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,45 +1224,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127836856</v>
+        <v>127835362</v>
       </c>
       <c r="B7" t="n">
-        <v>92631</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571858</v>
+        <v>571922</v>
       </c>
       <c r="R7" t="n">
-        <v>7078617</v>
+        <v>7078336</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1309,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,12 +1329,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1344,7 +1344,7 @@
         <v>127838430</v>
       </c>
       <c r="B8" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>127837929</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>127836491</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>127837975</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,45 +1789,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127837171</v>
+        <v>127836170</v>
       </c>
       <c r="B12" t="n">
-        <v>78782</v>
+        <v>92639</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571911</v>
+        <v>571920</v>
       </c>
       <c r="R12" t="n">
-        <v>7078553</v>
+        <v>7078374</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,45 +1896,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127836170</v>
+        <v>127837620</v>
       </c>
       <c r="B13" t="n">
-        <v>92631</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571920</v>
+        <v>572003</v>
       </c>
       <c r="R13" t="n">
-        <v>7078374</v>
+        <v>7078559</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,10 +2003,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127837620</v>
+        <v>127837171</v>
       </c>
       <c r="B14" t="n">
-        <v>79023</v>
+        <v>78788</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,21 +2014,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572003</v>
+        <v>571911</v>
       </c>
       <c r="R14" t="n">
-        <v>7078559</v>
+        <v>7078553</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,45 +2110,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127837382</v>
+        <v>127839625</v>
       </c>
       <c r="B15" t="n">
-        <v>92631</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571975</v>
+        <v>572022</v>
       </c>
       <c r="R15" t="n">
-        <v>7078587</v>
+        <v>7078301</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2180,7 +2185,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2190,7 +2195,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2217,50 +2227,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127839625</v>
+        <v>127837382</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>92639</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572022</v>
+        <v>571975</v>
       </c>
       <c r="R16" t="n">
-        <v>7078301</v>
+        <v>7078587</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2292,7 +2297,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2302,12 +2307,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,7 +2337,7 @@
         <v>127839595</v>
       </c>
       <c r="B17" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>127837562</v>
       </c>
       <c r="B18" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>127836801</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>127835846</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>127836645</v>
       </c>
       <c r="B21" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>127837292</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>127838341</v>
       </c>
       <c r="B23" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>127837312</v>
       </c>
       <c r="B24" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>127839604</v>
       </c>
       <c r="B25" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>127835378</v>
       </c>
       <c r="B26" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>127836444</v>
       </c>
       <c r="B27" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3571,32 +3571,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127837626</v>
+        <v>127837089</v>
       </c>
       <c r="B28" t="n">
-        <v>78781</v>
+        <v>92639</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571995</v>
+        <v>571919</v>
       </c>
       <c r="R28" t="n">
-        <v>7078559</v>
+        <v>7078558</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3678,32 +3678,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127837089</v>
+        <v>127837626</v>
       </c>
       <c r="B29" t="n">
-        <v>92631</v>
+        <v>78787</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571919</v>
+        <v>571995</v>
       </c>
       <c r="R29" t="n">
-        <v>7078558</v>
+        <v>7078559</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3788,7 +3788,7 @@
         <v>127838414</v>
       </c>
       <c r="B30" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>127837719</v>
       </c>
       <c r="B31" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4019,45 +4019,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127837544</v>
+        <v>127839665</v>
       </c>
       <c r="B32" t="n">
-        <v>79023</v>
+        <v>92639</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571972</v>
+        <v>572000</v>
       </c>
       <c r="R32" t="n">
-        <v>7078577</v>
+        <v>7078322</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4114,57 +4114,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127839665</v>
+        <v>127837544</v>
       </c>
       <c r="B33" t="n">
-        <v>92631</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572000</v>
+        <v>571972</v>
       </c>
       <c r="R33" t="n">
-        <v>7078322</v>
+        <v>7078577</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4221,12 +4221,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4236,7 +4236,7 @@
         <v>127837406</v>
       </c>
       <c r="B34" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>127836771</v>
       </c>
       <c r="B35" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>127837781</v>
       </c>
       <c r="B36" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -1010,45 +1010,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127836515</v>
+        <v>127835362</v>
       </c>
       <c r="B5" t="n">
-        <v>92639</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571804</v>
+        <v>571922</v>
       </c>
       <c r="R5" t="n">
-        <v>7078630</v>
+        <v>7078336</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1095,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,22 +1115,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127836856</v>
+        <v>127836515</v>
       </c>
       <c r="B6" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571858</v>
+        <v>571804</v>
       </c>
       <c r="R6" t="n">
-        <v>7078617</v>
+        <v>7078630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1197,7 +1207,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,50 +1234,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127835362</v>
+        <v>127836856</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571922</v>
+        <v>571858</v>
       </c>
       <c r="R7" t="n">
-        <v>7078336</v>
+        <v>7078617</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,12 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,12 +1329,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127836491</v>
+        <v>127837975</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,34 +1576,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571822</v>
+        <v>572082</v>
       </c>
       <c r="R10" t="n">
-        <v>7078604</v>
+        <v>7078455</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,7 +1640,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1645,7 +1650,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,22 +1670,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127837975</v>
+        <v>127836491</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,39 +1693,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572082</v>
+        <v>571822</v>
       </c>
       <c r="R11" t="n">
-        <v>7078455</v>
+        <v>7078604</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,7 +1752,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1757,12 +1762,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:33</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1777,12 +1777,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1792,7 +1792,7 @@
         <v>127836170</v>
       </c>
       <c r="B12" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2110,50 +2110,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127839625</v>
+        <v>127837382</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572022</v>
+        <v>571975</v>
       </c>
       <c r="R15" t="n">
-        <v>7078301</v>
+        <v>7078587</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,7 +2180,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2195,12 +2190,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2227,45 +2217,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127837382</v>
+        <v>127839625</v>
       </c>
       <c r="B16" t="n">
-        <v>92639</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571975</v>
+        <v>572022</v>
       </c>
       <c r="R16" t="n">
-        <v>7078587</v>
+        <v>7078301</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,7 +2292,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2307,7 +2302,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2444,7 +2444,7 @@
         <v>127837562</v>
       </c>
       <c r="B18" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>127836645</v>
       </c>
       <c r="B21" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>127837312</v>
       </c>
       <c r="B24" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3571,32 +3571,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127837089</v>
+        <v>127837626</v>
       </c>
       <c r="B28" t="n">
-        <v>92639</v>
+        <v>78787</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571919</v>
+        <v>571995</v>
       </c>
       <c r="R28" t="n">
-        <v>7078558</v>
+        <v>7078559</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3678,32 +3678,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127837626</v>
+        <v>127837089</v>
       </c>
       <c r="B29" t="n">
-        <v>78787</v>
+        <v>92640</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571995</v>
+        <v>571919</v>
       </c>
       <c r="R29" t="n">
-        <v>7078559</v>
+        <v>7078558</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4022,7 +4022,7 @@
         <v>127839665</v>
       </c>
       <c r="B32" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>127836771</v>
       </c>
       <c r="B35" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -1789,45 +1789,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127836170</v>
+        <v>127837620</v>
       </c>
       <c r="B12" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571920</v>
+        <v>572003</v>
       </c>
       <c r="R12" t="n">
-        <v>7078374</v>
+        <v>7078559</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,45 +1896,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127837620</v>
+        <v>127836170</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572003</v>
+        <v>571920</v>
       </c>
       <c r="R13" t="n">
-        <v>7078559</v>
+        <v>7078374</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2110,45 +2110,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127837382</v>
+        <v>127839625</v>
       </c>
       <c r="B15" t="n">
-        <v>92640</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571975</v>
+        <v>572022</v>
       </c>
       <c r="R15" t="n">
-        <v>7078587</v>
+        <v>7078301</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2180,7 +2185,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2190,7 +2195,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2217,50 +2227,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127839625</v>
+        <v>127837382</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572022</v>
+        <v>571975</v>
       </c>
       <c r="R16" t="n">
-        <v>7078301</v>
+        <v>7078587</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2292,7 +2297,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2302,12 +2307,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2441,45 +2441,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127837562</v>
+        <v>127836801</v>
       </c>
       <c r="B18" t="n">
-        <v>92640</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571988</v>
+        <v>571857</v>
       </c>
       <c r="R18" t="n">
-        <v>7078571</v>
+        <v>7078617</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,7 +2516,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2521,7 +2526,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2536,19 +2546,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127836801</v>
+        <v>127835846</v>
       </c>
       <c r="B19" t="n">
         <v>57672</v>
@@ -2584,14 +2594,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571857</v>
+        <v>571950</v>
       </c>
       <c r="R19" t="n">
-        <v>7078617</v>
+        <v>7078282</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,7 +2633,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2633,7 +2643,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2665,50 +2675,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127835846</v>
+        <v>127837562</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571950</v>
+        <v>571988</v>
       </c>
       <c r="R20" t="n">
-        <v>7078282</v>
+        <v>7078571</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2740,7 +2745,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2750,12 +2755,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,12 +2770,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3571,32 +3571,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127837626</v>
+        <v>127837089</v>
       </c>
       <c r="B28" t="n">
-        <v>78787</v>
+        <v>92640</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571995</v>
+        <v>571919</v>
       </c>
       <c r="R28" t="n">
-        <v>7078559</v>
+        <v>7078558</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3678,32 +3678,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127837089</v>
+        <v>127837626</v>
       </c>
       <c r="B29" t="n">
-        <v>92640</v>
+        <v>78787</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571919</v>
+        <v>571995</v>
       </c>
       <c r="R29" t="n">
-        <v>7078558</v>
+        <v>7078559</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -1010,50 +1010,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127835362</v>
+        <v>127836515</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>92641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571922</v>
+        <v>571804</v>
       </c>
       <c r="R5" t="n">
-        <v>7078336</v>
+        <v>7078630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,12 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,22 +1105,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127836515</v>
+        <v>127836856</v>
       </c>
       <c r="B6" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1162,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571804</v>
+        <v>571858</v>
       </c>
       <c r="R6" t="n">
-        <v>7078630</v>
+        <v>7078617</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1187,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,7 +1197,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,45 +1224,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127836856</v>
+        <v>127835362</v>
       </c>
       <c r="B7" t="n">
-        <v>92640</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571858</v>
+        <v>571922</v>
       </c>
       <c r="R7" t="n">
-        <v>7078617</v>
+        <v>7078336</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1309,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,12 +1329,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1789,45 +1789,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127837620</v>
+        <v>127836170</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>92641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572003</v>
+        <v>571920</v>
       </c>
       <c r="R12" t="n">
-        <v>7078559</v>
+        <v>7078374</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,45 +1896,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127836170</v>
+        <v>127837620</v>
       </c>
       <c r="B13" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571920</v>
+        <v>572003</v>
       </c>
       <c r="R13" t="n">
-        <v>7078374</v>
+        <v>7078559</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2110,50 +2110,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127839625</v>
+        <v>127837382</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>92641</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572022</v>
+        <v>571975</v>
       </c>
       <c r="R15" t="n">
-        <v>7078301</v>
+        <v>7078587</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,7 +2180,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2195,12 +2190,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2227,45 +2217,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127837382</v>
+        <v>127839625</v>
       </c>
       <c r="B16" t="n">
-        <v>92640</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571975</v>
+        <v>572022</v>
       </c>
       <c r="R16" t="n">
-        <v>7078587</v>
+        <v>7078301</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,7 +2292,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2307,7 +2302,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2441,50 +2441,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127836801</v>
+        <v>127837562</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>92641</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571857</v>
+        <v>571988</v>
       </c>
       <c r="R18" t="n">
-        <v>7078617</v>
+        <v>7078571</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2516,7 +2511,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2526,12 +2521,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2546,19 +2536,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127835846</v>
+        <v>127836801</v>
       </c>
       <c r="B19" t="n">
         <v>57672</v>
@@ -2594,14 +2584,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571950</v>
+        <v>571857</v>
       </c>
       <c r="R19" t="n">
-        <v>7078282</v>
+        <v>7078617</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2633,7 +2623,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2643,7 +2633,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2675,45 +2665,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127837562</v>
+        <v>127835846</v>
       </c>
       <c r="B20" t="n">
-        <v>92640</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571988</v>
+        <v>571950</v>
       </c>
       <c r="R20" t="n">
-        <v>7078571</v>
+        <v>7078282</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2745,7 +2740,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2755,7 +2750,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,57 +2770,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127836645</v>
+        <v>127837292</v>
       </c>
       <c r="B21" t="n">
-        <v>92640</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571821</v>
+        <v>571959</v>
       </c>
       <c r="R21" t="n">
-        <v>7078612</v>
+        <v>7078569</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2852,7 +2857,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2862,7 +2867,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2877,19 +2887,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127837292</v>
+        <v>127838341</v>
       </c>
       <c r="B22" t="n">
         <v>57672</v>
@@ -2925,14 +2935,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571959</v>
+        <v>572114</v>
       </c>
       <c r="R22" t="n">
-        <v>7078569</v>
+        <v>7078380</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2964,7 +2974,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2974,7 +2984,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3006,50 +3016,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127838341</v>
+        <v>127836645</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>92641</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572114</v>
+        <v>571821</v>
       </c>
       <c r="R23" t="n">
-        <v>7078380</v>
+        <v>7078612</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3081,7 +3086,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3091,12 +3096,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3111,12 +3111,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3126,7 +3126,7 @@
         <v>127837312</v>
       </c>
       <c r="B24" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>127837089</v>
       </c>
       <c r="B28" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>127839665</v>
       </c>
       <c r="B32" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>127836771</v>
       </c>
       <c r="B35" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -1010,45 +1010,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127836515</v>
+        <v>127835362</v>
       </c>
       <c r="B5" t="n">
-        <v>92641</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571804</v>
+        <v>571922</v>
       </c>
       <c r="R5" t="n">
-        <v>7078630</v>
+        <v>7078336</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1095,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,22 +1115,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127836856</v>
+        <v>127836515</v>
       </c>
       <c r="B6" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571858</v>
+        <v>571804</v>
       </c>
       <c r="R6" t="n">
-        <v>7078617</v>
+        <v>7078630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1197,7 +1207,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,50 +1234,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127835362</v>
+        <v>127836856</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571922</v>
+        <v>571858</v>
       </c>
       <c r="R7" t="n">
-        <v>7078336</v>
+        <v>7078617</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,12 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,12 +1329,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127837975</v>
+        <v>127836491</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,39 +1576,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572082</v>
+        <v>571822</v>
       </c>
       <c r="R10" t="n">
-        <v>7078455</v>
+        <v>7078604</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,7 +1635,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1650,12 +1645,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:33</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,22 +1660,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127836491</v>
+        <v>127837975</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,34 +1683,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571822</v>
+        <v>572082</v>
       </c>
       <c r="R11" t="n">
-        <v>7078604</v>
+        <v>7078455</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,7 +1747,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1762,7 +1757,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1777,12 +1777,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1792,7 +1792,7 @@
         <v>127836170</v>
       </c>
       <c r="B12" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127837620</v>
+        <v>127837171</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,21 +1907,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572003</v>
+        <v>571911</v>
       </c>
       <c r="R13" t="n">
-        <v>7078559</v>
+        <v>7078553</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,10 +2003,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127837171</v>
+        <v>127837620</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,21 +2014,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571911</v>
+        <v>572003</v>
       </c>
       <c r="R14" t="n">
-        <v>7078553</v>
+        <v>7078559</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,7 +2113,7 @@
         <v>127837382</v>
       </c>
       <c r="B15" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2441,45 +2441,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127837562</v>
+        <v>127836801</v>
       </c>
       <c r="B18" t="n">
-        <v>92641</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571988</v>
+        <v>571857</v>
       </c>
       <c r="R18" t="n">
-        <v>7078571</v>
+        <v>7078617</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,7 +2516,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2521,7 +2526,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2536,19 +2546,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127836801</v>
+        <v>127835846</v>
       </c>
       <c r="B19" t="n">
         <v>57672</v>
@@ -2584,14 +2594,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571857</v>
+        <v>571950</v>
       </c>
       <c r="R19" t="n">
-        <v>7078617</v>
+        <v>7078282</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,7 +2633,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2633,7 +2643,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2665,50 +2675,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127835846</v>
+        <v>127837562</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571950</v>
+        <v>571988</v>
       </c>
       <c r="R20" t="n">
-        <v>7078282</v>
+        <v>7078571</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2740,7 +2745,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2750,12 +2755,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,62 +2770,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127837292</v>
+        <v>127836645</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571959</v>
+        <v>571821</v>
       </c>
       <c r="R21" t="n">
-        <v>7078569</v>
+        <v>7078612</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2857,7 +2852,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2867,12 +2862,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2887,19 +2877,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127838341</v>
+        <v>127837292</v>
       </c>
       <c r="B22" t="n">
         <v>57672</v>
@@ -2935,14 +2925,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>572114</v>
+        <v>571959</v>
       </c>
       <c r="R22" t="n">
-        <v>7078380</v>
+        <v>7078569</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2974,7 +2964,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2984,7 +2974,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3016,45 +3006,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127836645</v>
+        <v>127838341</v>
       </c>
       <c r="B23" t="n">
-        <v>92641</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571821</v>
+        <v>572114</v>
       </c>
       <c r="R23" t="n">
-        <v>7078612</v>
+        <v>7078380</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3086,7 +3081,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3096,7 +3091,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3111,12 +3111,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3126,7 +3126,7 @@
         <v>127837312</v>
       </c>
       <c r="B24" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>127837089</v>
       </c>
       <c r="B28" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>127839665</v>
       </c>
       <c r="B32" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>127836771</v>
       </c>
       <c r="B35" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -1010,50 +1010,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127835362</v>
+        <v>127836856</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571922</v>
+        <v>571858</v>
       </c>
       <c r="R5" t="n">
-        <v>7078336</v>
+        <v>7078617</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,12 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,12 +1105,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1234,45 +1224,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127836856</v>
+        <v>127835362</v>
       </c>
       <c r="B7" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571858</v>
+        <v>571922</v>
       </c>
       <c r="R7" t="n">
-        <v>7078617</v>
+        <v>7078336</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1309,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,12 +1329,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127837171</v>
+        <v>127837620</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,21 +1907,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571911</v>
+        <v>572003</v>
       </c>
       <c r="R13" t="n">
-        <v>7078553</v>
+        <v>7078559</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,10 +2003,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127837620</v>
+        <v>127837171</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,21 +2014,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572003</v>
+        <v>571911</v>
       </c>
       <c r="R14" t="n">
-        <v>7078559</v>
+        <v>7078553</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,45 +2110,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127837382</v>
+        <v>127839625</v>
       </c>
       <c r="B15" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571975</v>
+        <v>572022</v>
       </c>
       <c r="R15" t="n">
-        <v>7078587</v>
+        <v>7078301</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2180,7 +2185,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2190,7 +2195,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2217,50 +2227,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127839625</v>
+        <v>127837382</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572022</v>
+        <v>571975</v>
       </c>
       <c r="R16" t="n">
-        <v>7078301</v>
+        <v>7078587</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2292,7 +2297,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2302,12 +2307,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2441,7 +2441,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127836801</v>
+        <v>127835846</v>
       </c>
       <c r="B18" t="n">
         <v>57672</v>
@@ -2477,14 +2477,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571857</v>
+        <v>571950</v>
       </c>
       <c r="R18" t="n">
-        <v>7078617</v>
+        <v>7078282</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2558,7 +2558,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127835846</v>
+        <v>127836801</v>
       </c>
       <c r="B19" t="n">
         <v>57672</v>
@@ -2594,14 +2594,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571950</v>
+        <v>571857</v>
       </c>
       <c r="R19" t="n">
-        <v>7078282</v>
+        <v>7078617</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -2441,50 +2441,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127835846</v>
+        <v>127837562</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571950</v>
+        <v>571988</v>
       </c>
       <c r="R18" t="n">
-        <v>7078282</v>
+        <v>7078571</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2516,7 +2511,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2526,12 +2521,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2546,19 +2536,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127836801</v>
+        <v>127835846</v>
       </c>
       <c r="B19" t="n">
         <v>57672</v>
@@ -2594,14 +2584,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571857</v>
+        <v>571950</v>
       </c>
       <c r="R19" t="n">
-        <v>7078617</v>
+        <v>7078282</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2633,7 +2623,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2643,7 +2633,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2675,45 +2665,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127837562</v>
+        <v>127836801</v>
       </c>
       <c r="B20" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571988</v>
+        <v>571857</v>
       </c>
       <c r="R20" t="n">
-        <v>7078571</v>
+        <v>7078617</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2745,7 +2740,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2755,7 +2750,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,12 +2770,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3123,45 +3123,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127837312</v>
+        <v>127839604</v>
       </c>
       <c r="B24" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571968</v>
+        <v>572030</v>
       </c>
       <c r="R24" t="n">
-        <v>7078566</v>
+        <v>7078309</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3193,7 +3198,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3203,7 +3208,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3218,62 +3228,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127839604</v>
+        <v>127837312</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572030</v>
+        <v>571968</v>
       </c>
       <c r="R25" t="n">
-        <v>7078309</v>
+        <v>7078566</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3305,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3315,12 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,12 +3335,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -2441,45 +2441,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127837562</v>
+        <v>127835846</v>
       </c>
       <c r="B18" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571988</v>
+        <v>571950</v>
       </c>
       <c r="R18" t="n">
-        <v>7078571</v>
+        <v>7078282</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,7 +2516,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2521,7 +2526,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2536,19 +2546,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127835846</v>
+        <v>127836801</v>
       </c>
       <c r="B19" t="n">
         <v>57672</v>
@@ -2584,14 +2594,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571950</v>
+        <v>571857</v>
       </c>
       <c r="R19" t="n">
-        <v>7078282</v>
+        <v>7078617</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,7 +2633,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2633,7 +2643,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2665,50 +2675,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127836801</v>
+        <v>127837562</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571857</v>
+        <v>571988</v>
       </c>
       <c r="R20" t="n">
-        <v>7078617</v>
+        <v>7078571</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2740,7 +2745,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2750,12 +2755,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,12 +2770,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3123,50 +3123,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127839604</v>
+        <v>127837312</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572030</v>
+        <v>571968</v>
       </c>
       <c r="R24" t="n">
-        <v>7078309</v>
+        <v>7078566</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3198,7 +3193,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3208,12 +3203,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3228,57 +3218,62 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127837312</v>
+        <v>127839604</v>
       </c>
       <c r="B25" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571968</v>
+        <v>572030</v>
       </c>
       <c r="R25" t="n">
-        <v>7078566</v>
+        <v>7078309</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3305,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3315,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,12 +3335,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -3123,45 +3123,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127837312</v>
+        <v>127839604</v>
       </c>
       <c r="B24" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571968</v>
+        <v>572030</v>
       </c>
       <c r="R24" t="n">
-        <v>7078566</v>
+        <v>7078309</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3193,7 +3198,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3203,7 +3208,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3218,62 +3228,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127839604</v>
+        <v>127837312</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572030</v>
+        <v>571968</v>
       </c>
       <c r="R25" t="n">
-        <v>7078309</v>
+        <v>7078566</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3305,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3315,12 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,12 +3335,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -3123,50 +3123,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127839604</v>
+        <v>127837312</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572030</v>
+        <v>571968</v>
       </c>
       <c r="R24" t="n">
-        <v>7078309</v>
+        <v>7078566</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3198,7 +3193,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3208,12 +3203,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3228,57 +3218,62 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127837312</v>
+        <v>127839604</v>
       </c>
       <c r="B25" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571968</v>
+        <v>572030</v>
       </c>
       <c r="R25" t="n">
-        <v>7078566</v>
+        <v>7078309</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3305,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3315,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,12 +3335,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>127838069</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>127836856</v>
       </c>
       <c r="B5" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>127836515</v>
       </c>
       <c r="B6" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>127835362</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>127838430</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>78791</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>127837929</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>127836491</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>127837975</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>127836170</v>
       </c>
       <c r="B12" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>127837620</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>127837171</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>78791</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,50 +2110,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127839625</v>
+        <v>127837382</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>92650</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572022</v>
+        <v>571975</v>
       </c>
       <c r="R15" t="n">
-        <v>7078301</v>
+        <v>7078587</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,7 +2180,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2195,12 +2190,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2227,45 +2217,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127837382</v>
+        <v>127839625</v>
       </c>
       <c r="B16" t="n">
-        <v>92642</v>
+        <v>57673</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571975</v>
+        <v>572022</v>
       </c>
       <c r="R16" t="n">
-        <v>7078587</v>
+        <v>7078301</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,7 +2292,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2307,7 +2302,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,7 +2337,7 @@
         <v>127839595</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>78791</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127835846</v>
+        <v>127836801</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2477,14 +2477,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571950</v>
+        <v>571857</v>
       </c>
       <c r="R18" t="n">
-        <v>7078282</v>
+        <v>7078617</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2558,10 +2558,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127836801</v>
+        <v>127835846</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,14 +2594,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571857</v>
+        <v>571950</v>
       </c>
       <c r="R19" t="n">
-        <v>7078617</v>
+        <v>7078282</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2678,7 +2678,7 @@
         <v>127837562</v>
       </c>
       <c r="B20" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>127836645</v>
       </c>
       <c r="B21" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>127837292</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>127838341</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>127837312</v>
       </c>
       <c r="B24" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>127839604</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>127835378</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>127836444</v>
       </c>
       <c r="B27" t="n">
-        <v>78788</v>
+        <v>78791</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3571,32 +3571,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127837089</v>
+        <v>127837626</v>
       </c>
       <c r="B28" t="n">
-        <v>92642</v>
+        <v>78790</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571919</v>
+        <v>571995</v>
       </c>
       <c r="R28" t="n">
-        <v>7078558</v>
+        <v>7078559</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3678,32 +3678,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127837626</v>
+        <v>127837089</v>
       </c>
       <c r="B29" t="n">
-        <v>78787</v>
+        <v>92650</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571995</v>
+        <v>571919</v>
       </c>
       <c r="R29" t="n">
-        <v>7078559</v>
+        <v>7078558</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3788,7 +3788,7 @@
         <v>127838414</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>127837719</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>127839665</v>
       </c>
       <c r="B32" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>127837544</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>127837406</v>
       </c>
       <c r="B34" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>127836771</v>
       </c>
       <c r="B35" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>127837781</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -1789,45 +1789,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127836170</v>
+        <v>127837171</v>
       </c>
       <c r="B12" t="n">
-        <v>92650</v>
+        <v>78791</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571920</v>
+        <v>571911</v>
       </c>
       <c r="R12" t="n">
-        <v>7078374</v>
+        <v>7078553</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,45 +1896,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127837620</v>
+        <v>127836170</v>
       </c>
       <c r="B13" t="n">
-        <v>79032</v>
+        <v>92650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572003</v>
+        <v>571920</v>
       </c>
       <c r="R13" t="n">
-        <v>7078559</v>
+        <v>7078374</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,10 +2003,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127837171</v>
+        <v>127837620</v>
       </c>
       <c r="B14" t="n">
-        <v>78791</v>
+        <v>79032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,21 +2014,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571911</v>
+        <v>572003</v>
       </c>
       <c r="R14" t="n">
-        <v>7078553</v>
+        <v>7078559</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2782,45 +2782,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127836645</v>
+        <v>127837292</v>
       </c>
       <c r="B21" t="n">
-        <v>92650</v>
+        <v>57673</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571821</v>
+        <v>571959</v>
       </c>
       <c r="R21" t="n">
-        <v>7078612</v>
+        <v>7078569</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2852,7 +2857,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2862,7 +2867,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2877,19 +2887,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127837292</v>
+        <v>127838341</v>
       </c>
       <c r="B22" t="n">
         <v>57673</v>
@@ -2925,14 +2935,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571959</v>
+        <v>572114</v>
       </c>
       <c r="R22" t="n">
-        <v>7078569</v>
+        <v>7078380</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2964,7 +2974,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2974,7 +2984,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3006,50 +3016,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127838341</v>
+        <v>127836645</v>
       </c>
       <c r="B23" t="n">
-        <v>57673</v>
+        <v>92650</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572114</v>
+        <v>571821</v>
       </c>
       <c r="R23" t="n">
-        <v>7078380</v>
+        <v>7078612</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3081,7 +3086,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3091,12 +3096,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3111,12 +3111,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3571,32 +3571,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127837626</v>
+        <v>127837089</v>
       </c>
       <c r="B28" t="n">
-        <v>78790</v>
+        <v>92650</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571995</v>
+        <v>571919</v>
       </c>
       <c r="R28" t="n">
-        <v>7078559</v>
+        <v>7078558</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3678,32 +3678,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127837089</v>
+        <v>127837626</v>
       </c>
       <c r="B29" t="n">
-        <v>92650</v>
+        <v>78790</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571919</v>
+        <v>571995</v>
       </c>
       <c r="R29" t="n">
-        <v>7078558</v>
+        <v>7078559</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>127838069</v>
       </c>
       <c r="B4" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127836856</v>
+        <v>127836515</v>
       </c>
       <c r="B5" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571858</v>
+        <v>571804</v>
       </c>
       <c r="R5" t="n">
-        <v>7078617</v>
+        <v>7078630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127836515</v>
+        <v>127836856</v>
       </c>
       <c r="B6" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571804</v>
+        <v>571858</v>
       </c>
       <c r="R6" t="n">
-        <v>7078630</v>
+        <v>7078617</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,7 +1227,7 @@
         <v>127835362</v>
       </c>
       <c r="B7" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>127838430</v>
       </c>
       <c r="B8" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>127837929</v>
       </c>
       <c r="B9" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>127836491</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>127837975</v>
       </c>
       <c r="B11" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,45 +1789,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127837171</v>
+        <v>127836170</v>
       </c>
       <c r="B12" t="n">
-        <v>78791</v>
+        <v>92742</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571911</v>
+        <v>571920</v>
       </c>
       <c r="R12" t="n">
-        <v>7078553</v>
+        <v>7078374</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,45 +1896,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127836170</v>
+        <v>127837620</v>
       </c>
       <c r="B13" t="n">
-        <v>92650</v>
+        <v>79083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571920</v>
+        <v>572003</v>
       </c>
       <c r="R13" t="n">
-        <v>7078374</v>
+        <v>7078559</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,10 +2003,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127837620</v>
+        <v>127837171</v>
       </c>
       <c r="B14" t="n">
-        <v>79032</v>
+        <v>78841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,21 +2014,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572003</v>
+        <v>571911</v>
       </c>
       <c r="R14" t="n">
-        <v>7078559</v>
+        <v>7078553</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,7 +2113,7 @@
         <v>127837382</v>
       </c>
       <c r="B15" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>127839625</v>
       </c>
       <c r="B16" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>127839595</v>
       </c>
       <c r="B17" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>127836801</v>
       </c>
       <c r="B18" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>127835846</v>
       </c>
       <c r="B19" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>127837562</v>
       </c>
       <c r="B20" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>127837292</v>
       </c>
       <c r="B21" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>127838341</v>
       </c>
       <c r="B22" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>127836645</v>
       </c>
       <c r="B23" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>127837312</v>
       </c>
       <c r="B24" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>127839604</v>
       </c>
       <c r="B25" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3347,10 +3347,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127835378</v>
+        <v>127836444</v>
       </c>
       <c r="B26" t="n">
-        <v>57673</v>
+        <v>78841</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,39 +3358,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571927</v>
+        <v>571831</v>
       </c>
       <c r="R26" t="n">
-        <v>7078333</v>
+        <v>7078599</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3422,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3432,12 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3452,22 +3442,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127836444</v>
+        <v>127835378</v>
       </c>
       <c r="B27" t="n">
-        <v>78791</v>
+        <v>57685</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,34 +3465,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571831</v>
+        <v>571927</v>
       </c>
       <c r="R27" t="n">
-        <v>7078599</v>
+        <v>7078333</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3534,7 +3529,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3544,7 +3539,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3559,12 +3559,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3574,7 +3574,7 @@
         <v>127837089</v>
       </c>
       <c r="B28" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>127837626</v>
       </c>
       <c r="B29" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>127838414</v>
       </c>
       <c r="B30" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>127837719</v>
       </c>
       <c r="B31" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4019,45 +4019,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127839665</v>
+        <v>127837544</v>
       </c>
       <c r="B32" t="n">
-        <v>92650</v>
+        <v>79083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572000</v>
+        <v>571972</v>
       </c>
       <c r="R32" t="n">
-        <v>7078322</v>
+        <v>7078577</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4114,57 +4114,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127837544</v>
+        <v>127839665</v>
       </c>
       <c r="B33" t="n">
-        <v>79032</v>
+        <v>92742</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571972</v>
+        <v>572000</v>
       </c>
       <c r="R33" t="n">
-        <v>7078577</v>
+        <v>7078322</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4221,12 +4221,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4236,7 +4236,7 @@
         <v>127837406</v>
       </c>
       <c r="B34" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4349,45 +4349,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127836771</v>
+        <v>127837781</v>
       </c>
       <c r="B35" t="n">
-        <v>92650</v>
+        <v>57685</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>571861</v>
+        <v>572047</v>
       </c>
       <c r="R35" t="n">
-        <v>7078614</v>
+        <v>7078503</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4419,7 +4424,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4429,7 +4434,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4444,62 +4454,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127837781</v>
+        <v>127836771</v>
       </c>
       <c r="B36" t="n">
-        <v>57673</v>
+        <v>92742</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>572047</v>
+        <v>571861</v>
       </c>
       <c r="R36" t="n">
-        <v>7078503</v>
+        <v>7078614</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4531,7 +4536,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4541,12 +4546,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4561,12 +4561,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -2441,50 +2441,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127836801</v>
+        <v>127837562</v>
       </c>
       <c r="B18" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571857</v>
+        <v>571988</v>
       </c>
       <c r="R18" t="n">
-        <v>7078617</v>
+        <v>7078571</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2516,7 +2511,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2526,12 +2521,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2546,12 +2536,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2675,45 +2665,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127837562</v>
+        <v>127836801</v>
       </c>
       <c r="B20" t="n">
-        <v>92742</v>
+        <v>57685</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571988</v>
+        <v>571857</v>
       </c>
       <c r="R20" t="n">
-        <v>7078571</v>
+        <v>7078617</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2745,7 +2740,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2755,7 +2750,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,62 +2770,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127837292</v>
+        <v>127836645</v>
       </c>
       <c r="B21" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571959</v>
+        <v>571821</v>
       </c>
       <c r="R21" t="n">
-        <v>7078569</v>
+        <v>7078612</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2857,7 +2852,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2867,12 +2862,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2887,19 +2877,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127838341</v>
+        <v>127837292</v>
       </c>
       <c r="B22" t="n">
         <v>57685</v>
@@ -2935,14 +2925,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>572114</v>
+        <v>571959</v>
       </c>
       <c r="R22" t="n">
-        <v>7078380</v>
+        <v>7078569</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2974,7 +2964,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2984,7 +2974,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3016,45 +3006,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127836645</v>
+        <v>127838341</v>
       </c>
       <c r="B23" t="n">
-        <v>92742</v>
+        <v>57685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571821</v>
+        <v>572114</v>
       </c>
       <c r="R23" t="n">
-        <v>7078612</v>
+        <v>7078380</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3086,7 +3081,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3096,7 +3091,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3111,12 +3111,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3347,10 +3347,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127836444</v>
+        <v>127835378</v>
       </c>
       <c r="B26" t="n">
-        <v>78841</v>
+        <v>57685</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,34 +3358,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571831</v>
+        <v>571927</v>
       </c>
       <c r="R26" t="n">
-        <v>7078599</v>
+        <v>7078333</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3417,7 +3422,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3432,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3442,22 +3452,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127835378</v>
+        <v>127836444</v>
       </c>
       <c r="B27" t="n">
-        <v>57685</v>
+        <v>78841</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,39 +3475,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571927</v>
+        <v>571831</v>
       </c>
       <c r="R27" t="n">
-        <v>7078333</v>
+        <v>7078599</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3529,7 +3534,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3539,12 +3544,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3559,12 +3559,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4019,45 +4019,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127837544</v>
+        <v>127839665</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>92742</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571972</v>
+        <v>572000</v>
       </c>
       <c r="R32" t="n">
-        <v>7078577</v>
+        <v>7078322</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4114,57 +4114,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127839665</v>
+        <v>127837544</v>
       </c>
       <c r="B33" t="n">
-        <v>92742</v>
+        <v>79083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572000</v>
+        <v>571972</v>
       </c>
       <c r="R33" t="n">
-        <v>7078322</v>
+        <v>7078577</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4221,12 +4221,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4349,50 +4349,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127837781</v>
+        <v>127836771</v>
       </c>
       <c r="B35" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572047</v>
+        <v>571861</v>
       </c>
       <c r="R35" t="n">
-        <v>7078503</v>
+        <v>7078614</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4424,7 +4419,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4434,12 +4429,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4454,57 +4444,62 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127836771</v>
+        <v>127837781</v>
       </c>
       <c r="B36" t="n">
-        <v>92742</v>
+        <v>57685</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>571861</v>
+        <v>572047</v>
       </c>
       <c r="R36" t="n">
-        <v>7078614</v>
+        <v>7078503</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4536,7 +4531,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4546,7 +4541,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4561,12 +4561,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -3123,45 +3123,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127837312</v>
+        <v>127839604</v>
       </c>
       <c r="B24" t="n">
-        <v>92742</v>
+        <v>57685</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571968</v>
+        <v>572030</v>
       </c>
       <c r="R24" t="n">
-        <v>7078566</v>
+        <v>7078309</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3193,7 +3198,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3203,7 +3208,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3218,62 +3228,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127839604</v>
+        <v>127837312</v>
       </c>
       <c r="B25" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572030</v>
+        <v>571968</v>
       </c>
       <c r="R25" t="n">
-        <v>7078309</v>
+        <v>7078566</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3305,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3315,12 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,12 +3335,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3571,32 +3571,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127837089</v>
+        <v>127837626</v>
       </c>
       <c r="B28" t="n">
-        <v>92742</v>
+        <v>78840</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571919</v>
+        <v>571995</v>
       </c>
       <c r="R28" t="n">
-        <v>7078558</v>
+        <v>7078559</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3678,32 +3678,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127837626</v>
+        <v>127837089</v>
       </c>
       <c r="B29" t="n">
-        <v>78840</v>
+        <v>92742</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571995</v>
+        <v>571919</v>
       </c>
       <c r="R29" t="n">
-        <v>7078559</v>
+        <v>7078558</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -1789,45 +1789,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127836170</v>
+        <v>127837620</v>
       </c>
       <c r="B12" t="n">
-        <v>92742</v>
+        <v>79083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571920</v>
+        <v>572003</v>
       </c>
       <c r="R12" t="n">
-        <v>7078374</v>
+        <v>7078559</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127837620</v>
+        <v>127837171</v>
       </c>
       <c r="B13" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,21 +1907,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572003</v>
+        <v>571911</v>
       </c>
       <c r="R13" t="n">
-        <v>7078559</v>
+        <v>7078553</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,45 +2003,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127837171</v>
+        <v>127836170</v>
       </c>
       <c r="B14" t="n">
-        <v>78841</v>
+        <v>92742</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571911</v>
+        <v>571920</v>
       </c>
       <c r="R14" t="n">
-        <v>7078553</v>
+        <v>7078374</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3123,50 +3123,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127839604</v>
+        <v>127837312</v>
       </c>
       <c r="B24" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572030</v>
+        <v>571968</v>
       </c>
       <c r="R24" t="n">
-        <v>7078309</v>
+        <v>7078566</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3198,7 +3193,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3208,12 +3203,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3228,57 +3218,62 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127837312</v>
+        <v>127839604</v>
       </c>
       <c r="B25" t="n">
-        <v>92742</v>
+        <v>57685</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571968</v>
+        <v>572030</v>
       </c>
       <c r="R25" t="n">
-        <v>7078566</v>
+        <v>7078309</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3305,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3315,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,12 +3335,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -4019,45 +4019,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127839665</v>
+        <v>127837544</v>
       </c>
       <c r="B32" t="n">
-        <v>92742</v>
+        <v>79083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572000</v>
+        <v>571972</v>
       </c>
       <c r="R32" t="n">
-        <v>7078322</v>
+        <v>7078577</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4114,57 +4114,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127837544</v>
+        <v>127839665</v>
       </c>
       <c r="B33" t="n">
-        <v>79083</v>
+        <v>92742</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Källmyrtjärnen, Källmyrtjärnen, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571972</v>
+        <v>572000</v>
       </c>
       <c r="R33" t="n">
-        <v>7078577</v>
+        <v>7078322</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4221,12 +4221,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -4573,10 +4573,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128964288</v>
+        <v>128964493</v>
       </c>
       <c r="B37" t="n">
-        <v>57723</v>
+        <v>79653</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4584,39 +4584,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572121</v>
+        <v>572133</v>
       </c>
       <c r="R37" t="n">
-        <v>7078371</v>
+        <v>7078367</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4648,7 +4643,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4658,12 +4653,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4690,10 +4680,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128964493</v>
+        <v>128964288</v>
       </c>
       <c r="B38" t="n">
-        <v>79653</v>
+        <v>57723</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4701,34 +4691,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572133</v>
+        <v>572121</v>
       </c>
       <c r="R38" t="n">
-        <v>7078367</v>
+        <v>7078371</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4760,7 +4755,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4770,7 +4765,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -6794,48 +6794,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128968889</v>
+        <v>128967070</v>
       </c>
       <c r="B58" t="n">
-        <v>79034</v>
+        <v>92811</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572173</v>
+        <v>571779</v>
       </c>
       <c r="R58" t="n">
-        <v>7078310</v>
+        <v>7078375</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6862,14 +6862,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6884,22 +6889,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128964140</v>
+        <v>128968889</v>
       </c>
       <c r="B59" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6907,42 +6912,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572050</v>
+        <v>572173</v>
       </c>
       <c r="R59" t="n">
-        <v>7078406</v>
+        <v>7078310</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6969,24 +6969,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7001,19 +6991,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128963996</v>
+        <v>128964140</v>
       </c>
       <c r="B60" t="n">
         <v>57723</v>
@@ -7053,10 +7043,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572001</v>
+        <v>572050</v>
       </c>
       <c r="R60" t="n">
-        <v>7078333</v>
+        <v>7078406</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7088,7 +7078,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7098,7 +7088,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7118,57 +7108,62 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128967070</v>
+        <v>128963996</v>
       </c>
       <c r="B61" t="n">
-        <v>92811</v>
+        <v>57723</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>571779</v>
+        <v>572001</v>
       </c>
       <c r="R61" t="n">
-        <v>7078375</v>
+        <v>7078333</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7200,7 +7195,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7210,7 +7205,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7225,12 +7225,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7548,50 +7548,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128964634</v>
+        <v>128964295</v>
       </c>
       <c r="B65" t="n">
-        <v>57723</v>
+        <v>92811</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572167</v>
+        <v>572110</v>
       </c>
       <c r="R65" t="n">
-        <v>7078321</v>
+        <v>7078382</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7623,7 +7618,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7633,12 +7628,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7653,44 +7643,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128964295</v>
+        <v>128964587</v>
       </c>
       <c r="B66" t="n">
-        <v>92811</v>
+        <v>90552</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7700,10 +7690,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572110</v>
+        <v>572155</v>
       </c>
       <c r="R66" t="n">
-        <v>7078382</v>
+        <v>7078337</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7735,7 +7725,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7745,7 +7735,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7760,22 +7750,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128964587</v>
+        <v>128964712</v>
       </c>
       <c r="B67" t="n">
-        <v>90552</v>
+        <v>79034</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7783,21 +7773,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7807,10 +7797,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572155</v>
+        <v>572171</v>
       </c>
       <c r="R67" t="n">
-        <v>7078337</v>
+        <v>7078312</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7842,7 +7832,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7852,7 +7842,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7867,22 +7857,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128964712</v>
+        <v>128964634</v>
       </c>
       <c r="B68" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7890,34 +7880,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>572171</v>
+        <v>572167</v>
       </c>
       <c r="R68" t="n">
-        <v>7078312</v>
+        <v>7078321</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7949,7 +7944,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7959,7 +7954,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7974,12 +7974,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -4800,7 +4800,7 @@
         <v>128964085</v>
       </c>
       <c r="B39" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5108,48 +5108,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128963682</v>
+        <v>128968879</v>
       </c>
       <c r="B42" t="n">
-        <v>92815</v>
+        <v>57883</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571916</v>
+        <v>571970</v>
       </c>
       <c r="R42" t="n">
-        <v>7078360</v>
+        <v>7078312</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5176,19 +5176,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5203,60 +5193,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128968879</v>
+        <v>128963682</v>
       </c>
       <c r="B43" t="n">
-        <v>57883</v>
+        <v>92820</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>571970</v>
+        <v>571916</v>
       </c>
       <c r="R43" t="n">
-        <v>7078312</v>
+        <v>7078360</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5283,9 +5273,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5300,65 +5300,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128964321</v>
+        <v>128968893</v>
       </c>
       <c r="B44" t="n">
-        <v>78700</v>
+        <v>92816</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572123</v>
+        <v>571944</v>
       </c>
       <c r="R44" t="n">
-        <v>7078382</v>
+        <v>7078352</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5385,19 +5380,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5412,60 +5397,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128968893</v>
+        <v>128964321</v>
       </c>
       <c r="B45" t="n">
-        <v>92811</v>
+        <v>78700</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571944</v>
+        <v>572123</v>
       </c>
       <c r="R45" t="n">
-        <v>7078352</v>
+        <v>7078382</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5492,9 +5482,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5509,22 +5509,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128963835</v>
+        <v>128968897</v>
       </c>
       <c r="B46" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5552,17 +5552,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>571961</v>
+        <v>572106</v>
       </c>
       <c r="R46" t="n">
-        <v>7078380</v>
+        <v>7078370</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5589,19 +5589,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5616,22 +5606,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128968897</v>
+        <v>128964635</v>
       </c>
       <c r="B47" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5659,17 +5649,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572106</v>
+        <v>572167</v>
       </c>
       <c r="R47" t="n">
-        <v>7078370</v>
+        <v>7078311</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5696,9 +5686,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5713,44 +5713,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128963734</v>
+        <v>128963835</v>
       </c>
       <c r="B48" t="n">
-        <v>92805</v>
+        <v>92816</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5760,10 +5760,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>571951</v>
+        <v>571961</v>
       </c>
       <c r="R48" t="n">
-        <v>7078394</v>
+        <v>7078380</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5832,32 +5832,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128964635</v>
+        <v>128963734</v>
       </c>
       <c r="B49" t="n">
-        <v>92811</v>
+        <v>92810</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572167</v>
+        <v>571951</v>
       </c>
       <c r="R49" t="n">
-        <v>7078311</v>
+        <v>7078394</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5942,7 +5942,7 @@
         <v>128963876</v>
       </c>
       <c r="B50" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>128968900</v>
       </c>
       <c r="B51" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>128967046</v>
       </c>
       <c r="B52" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>128968899</v>
       </c>
       <c r="B53" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6464,10 +6464,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128963789</v>
+        <v>128964016</v>
       </c>
       <c r="B55" t="n">
-        <v>92805</v>
+        <v>92842</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6475,43 +6475,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>571944</v>
+        <v>572005</v>
       </c>
       <c r="R55" t="n">
-        <v>7078381</v>
+        <v>7078331</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6543,7 +6534,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6553,7 +6544,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6580,10 +6571,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128964016</v>
+        <v>128963789</v>
       </c>
       <c r="B56" t="n">
-        <v>92837</v>
+        <v>92810</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6591,34 +6582,43 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572005</v>
+        <v>571944</v>
       </c>
       <c r="R56" t="n">
-        <v>7078331</v>
+        <v>7078381</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6794,45 +6794,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128967070</v>
+        <v>128964140</v>
       </c>
       <c r="B58" t="n">
-        <v>92811</v>
+        <v>57723</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>571779</v>
+        <v>572050</v>
       </c>
       <c r="R58" t="n">
-        <v>7078375</v>
+        <v>7078406</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6864,7 +6869,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6874,7 +6879,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6901,48 +6911,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128968889</v>
+        <v>128967070</v>
       </c>
       <c r="B59" t="n">
-        <v>79034</v>
+        <v>92816</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572173</v>
+        <v>571779</v>
       </c>
       <c r="R59" t="n">
-        <v>7078310</v>
+        <v>7078375</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6969,14 +6979,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6991,22 +7006,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128964140</v>
+        <v>128968889</v>
       </c>
       <c r="B60" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7014,42 +7029,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572050</v>
+        <v>572173</v>
       </c>
       <c r="R60" t="n">
-        <v>7078406</v>
+        <v>7078310</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7076,24 +7086,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7108,12 +7108,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7240,7 +7240,7 @@
         <v>128968898</v>
       </c>
       <c r="B62" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>128964127</v>
       </c>
       <c r="B63" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>128964698</v>
       </c>
       <c r="B64" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>128964295</v>
       </c>
       <c r="B65" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>128964587</v>
       </c>
       <c r="B66" t="n">
-        <v>90552</v>
+        <v>90555</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>128968892</v>
       </c>
       <c r="B69" t="n">
-        <v>96140</v>
+        <v>96145</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -4573,10 +4573,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128964493</v>
+        <v>128964288</v>
       </c>
       <c r="B37" t="n">
-        <v>79653</v>
+        <v>57723</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4584,34 +4584,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572133</v>
+        <v>572121</v>
       </c>
       <c r="R37" t="n">
-        <v>7078367</v>
+        <v>7078371</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4643,7 +4648,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4653,7 +4658,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4680,10 +4690,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128964288</v>
+        <v>128964493</v>
       </c>
       <c r="B38" t="n">
-        <v>57723</v>
+        <v>79654</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4691,39 +4701,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572121</v>
+        <v>572133</v>
       </c>
       <c r="R38" t="n">
-        <v>7078371</v>
+        <v>7078367</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4755,7 +4760,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4765,12 +4770,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4800,7 +4800,7 @@
         <v>128964085</v>
       </c>
       <c r="B39" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>128968891</v>
       </c>
       <c r="B40" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>128964559</v>
       </c>
       <c r="B41" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>128963682</v>
       </c>
       <c r="B43" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5312,48 +5312,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128968893</v>
+        <v>128964321</v>
       </c>
       <c r="B44" t="n">
-        <v>92816</v>
+        <v>78701</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571944</v>
+        <v>572123</v>
       </c>
       <c r="R44" t="n">
-        <v>7078352</v>
+        <v>7078382</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5380,9 +5385,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5397,65 +5412,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128964321</v>
+        <v>128968893</v>
       </c>
       <c r="B45" t="n">
-        <v>78700</v>
+        <v>92819</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572123</v>
+        <v>571944</v>
       </c>
       <c r="R45" t="n">
-        <v>7078382</v>
+        <v>7078352</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5482,19 +5492,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5509,22 +5509,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128968897</v>
+        <v>128963835</v>
       </c>
       <c r="B46" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5552,17 +5552,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572106</v>
+        <v>571961</v>
       </c>
       <c r="R46" t="n">
-        <v>7078370</v>
+        <v>7078380</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5589,9 +5589,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5606,22 +5616,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128964635</v>
+        <v>128968897</v>
       </c>
       <c r="B47" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5649,17 +5659,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572167</v>
+        <v>572106</v>
       </c>
       <c r="R47" t="n">
-        <v>7078311</v>
+        <v>7078370</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5686,19 +5696,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5713,44 +5713,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128963835</v>
+        <v>128963734</v>
       </c>
       <c r="B48" t="n">
-        <v>92816</v>
+        <v>92813</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5760,10 +5760,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>571961</v>
+        <v>571951</v>
       </c>
       <c r="R48" t="n">
-        <v>7078380</v>
+        <v>7078394</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5832,32 +5832,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128963734</v>
+        <v>128964635</v>
       </c>
       <c r="B49" t="n">
-        <v>92810</v>
+        <v>92819</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>571951</v>
+        <v>572167</v>
       </c>
       <c r="R49" t="n">
-        <v>7078394</v>
+        <v>7078311</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5942,7 +5942,7 @@
         <v>128963876</v>
       </c>
       <c r="B50" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6046,48 +6046,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128968900</v>
+        <v>128967046</v>
       </c>
       <c r="B51" t="n">
-        <v>92816</v>
+        <v>92835</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>571998</v>
+        <v>571822</v>
       </c>
       <c r="R51" t="n">
-        <v>7078374</v>
+        <v>7078359</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6114,9 +6114,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6131,60 +6141,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128967046</v>
+        <v>128968900</v>
       </c>
       <c r="B52" t="n">
-        <v>92832</v>
+        <v>92819</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>571822</v>
+        <v>571998</v>
       </c>
       <c r="R52" t="n">
-        <v>7078359</v>
+        <v>7078374</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6211,19 +6221,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>17:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6238,12 +6238,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6253,7 +6253,7 @@
         <v>128968899</v>
       </c>
       <c r="B53" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>128964016</v>
       </c>
       <c r="B55" t="n">
-        <v>92842</v>
+        <v>92845</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6571,10 +6571,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128963789</v>
+        <v>128964488</v>
       </c>
       <c r="B56" t="n">
-        <v>92810</v>
+        <v>78792</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6582,43 +6582,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>571944</v>
+        <v>572134</v>
       </c>
       <c r="R56" t="n">
-        <v>7078381</v>
+        <v>7078366</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6650,7 +6641,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6660,7 +6651,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6687,10 +6678,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128964488</v>
+        <v>128963789</v>
       </c>
       <c r="B57" t="n">
-        <v>78791</v>
+        <v>92813</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6698,34 +6689,43 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572134</v>
+        <v>571944</v>
       </c>
       <c r="R57" t="n">
-        <v>7078366</v>
+        <v>7078381</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6794,10 +6794,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128964140</v>
+        <v>128968889</v>
       </c>
       <c r="B58" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6805,42 +6805,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572050</v>
+        <v>572173</v>
       </c>
       <c r="R58" t="n">
-        <v>7078406</v>
+        <v>7078310</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6867,24 +6862,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6899,12 +6884,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6914,7 +6899,7 @@
         <v>128967070</v>
       </c>
       <c r="B59" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7018,10 +7003,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128968889</v>
+        <v>128963996</v>
       </c>
       <c r="B60" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7029,37 +7014,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572173</v>
+        <v>572001</v>
       </c>
       <c r="R60" t="n">
-        <v>7078310</v>
+        <v>7078333</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7086,14 +7076,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7108,19 +7108,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128963996</v>
+        <v>128964140</v>
       </c>
       <c r="B61" t="n">
         <v>57723</v>
@@ -7160,10 +7160,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572001</v>
+        <v>572050</v>
       </c>
       <c r="R61" t="n">
-        <v>7078333</v>
+        <v>7078406</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -7225,12 +7225,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7240,7 +7240,7 @@
         <v>128968898</v>
       </c>
       <c r="B62" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>128964127</v>
       </c>
       <c r="B63" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>128964698</v>
       </c>
       <c r="B64" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7548,32 +7548,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128964295</v>
+        <v>128964587</v>
       </c>
       <c r="B65" t="n">
-        <v>92816</v>
+        <v>90558</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7583,10 +7583,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572110</v>
+        <v>572155</v>
       </c>
       <c r="R65" t="n">
-        <v>7078382</v>
+        <v>7078337</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7643,44 +7643,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128964587</v>
+        <v>128964295</v>
       </c>
       <c r="B66" t="n">
-        <v>90555</v>
+        <v>92819</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572155</v>
+        <v>572110</v>
       </c>
       <c r="R66" t="n">
-        <v>7078337</v>
+        <v>7078382</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7750,12 +7750,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7765,7 +7765,7 @@
         <v>128964712</v>
       </c>
       <c r="B67" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>128968892</v>
       </c>
       <c r="B69" t="n">
-        <v>96145</v>
+        <v>96148</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -4573,10 +4573,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128964288</v>
+        <v>128964493</v>
       </c>
       <c r="B37" t="n">
-        <v>57723</v>
+        <v>79654</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4584,39 +4584,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572121</v>
+        <v>572133</v>
       </c>
       <c r="R37" t="n">
-        <v>7078371</v>
+        <v>7078367</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4648,7 +4643,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4658,12 +4653,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4690,10 +4680,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128964493</v>
+        <v>128964288</v>
       </c>
       <c r="B38" t="n">
-        <v>79654</v>
+        <v>57723</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4701,34 +4691,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572133</v>
+        <v>572121</v>
       </c>
       <c r="R38" t="n">
-        <v>7078367</v>
+        <v>7078371</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4760,7 +4755,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4770,7 +4765,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5108,48 +5108,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128968879</v>
+        <v>128963682</v>
       </c>
       <c r="B42" t="n">
-        <v>57883</v>
+        <v>92823</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571970</v>
+        <v>571916</v>
       </c>
       <c r="R42" t="n">
-        <v>7078312</v>
+        <v>7078360</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5176,9 +5176,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5193,60 +5203,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128963682</v>
+        <v>128968879</v>
       </c>
       <c r="B43" t="n">
-        <v>92823</v>
+        <v>57883</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>571916</v>
+        <v>571970</v>
       </c>
       <c r="R43" t="n">
-        <v>7078360</v>
+        <v>7078312</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5273,19 +5283,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5300,65 +5300,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128964321</v>
+        <v>128968893</v>
       </c>
       <c r="B44" t="n">
-        <v>78701</v>
+        <v>92819</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572123</v>
+        <v>571944</v>
       </c>
       <c r="R44" t="n">
-        <v>7078382</v>
+        <v>7078352</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5385,19 +5380,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5412,60 +5397,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128968893</v>
+        <v>128964321</v>
       </c>
       <c r="B45" t="n">
-        <v>92819</v>
+        <v>78701</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571944</v>
+        <v>572123</v>
       </c>
       <c r="R45" t="n">
-        <v>7078352</v>
+        <v>7078382</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5492,9 +5482,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5509,12 +5509,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5628,48 +5628,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128968897</v>
+        <v>128963734</v>
       </c>
       <c r="B47" t="n">
-        <v>92819</v>
+        <v>92813</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572106</v>
+        <v>571951</v>
       </c>
       <c r="R47" t="n">
-        <v>7078370</v>
+        <v>7078394</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5696,9 +5696,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5713,44 +5723,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128963734</v>
+        <v>128964635</v>
       </c>
       <c r="B48" t="n">
-        <v>92813</v>
+        <v>92819</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5760,10 +5770,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>571951</v>
+        <v>572167</v>
       </c>
       <c r="R48" t="n">
-        <v>7078394</v>
+        <v>7078311</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5795,7 +5805,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5805,7 +5815,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5832,7 +5842,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128964635</v>
+        <v>128968897</v>
       </c>
       <c r="B49" t="n">
         <v>92819</v>
@@ -5863,17 +5873,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572167</v>
+        <v>572106</v>
       </c>
       <c r="R49" t="n">
-        <v>7078311</v>
+        <v>7078370</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5900,19 +5910,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5927,12 +5927,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6464,10 +6464,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128964016</v>
+        <v>128963789</v>
       </c>
       <c r="B55" t="n">
-        <v>92845</v>
+        <v>92813</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6475,34 +6475,43 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572005</v>
+        <v>571944</v>
       </c>
       <c r="R55" t="n">
-        <v>7078331</v>
+        <v>7078381</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6534,7 +6543,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6544,7 +6553,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6571,10 +6580,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128964488</v>
+        <v>128964016</v>
       </c>
       <c r="B56" t="n">
-        <v>78792</v>
+        <v>92845</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6582,21 +6591,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>5448</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6606,10 +6615,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572134</v>
+        <v>572005</v>
       </c>
       <c r="R56" t="n">
-        <v>7078366</v>
+        <v>7078331</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6641,7 +6650,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6651,7 +6660,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6678,10 +6687,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128963789</v>
+        <v>128964488</v>
       </c>
       <c r="B57" t="n">
-        <v>92813</v>
+        <v>78792</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6689,43 +6698,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>571944</v>
+        <v>572134</v>
       </c>
       <c r="R57" t="n">
-        <v>7078381</v>
+        <v>7078366</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6794,48 +6794,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128968889</v>
+        <v>128967070</v>
       </c>
       <c r="B58" t="n">
-        <v>79035</v>
+        <v>92819</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572173</v>
+        <v>571779</v>
       </c>
       <c r="R58" t="n">
-        <v>7078310</v>
+        <v>7078375</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6862,14 +6862,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6884,60 +6889,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128967070</v>
+        <v>128968889</v>
       </c>
       <c r="B59" t="n">
-        <v>92819</v>
+        <v>79035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>571779</v>
+        <v>572173</v>
       </c>
       <c r="R59" t="n">
-        <v>7078375</v>
+        <v>7078310</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6964,19 +6969,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>17:24</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6991,19 +6991,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128963996</v>
+        <v>128964140</v>
       </c>
       <c r="B60" t="n">
         <v>57723</v>
@@ -7043,10 +7043,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572001</v>
+        <v>572050</v>
       </c>
       <c r="R60" t="n">
-        <v>7078333</v>
+        <v>7078406</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7108,19 +7108,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128964140</v>
+        <v>128963996</v>
       </c>
       <c r="B61" t="n">
         <v>57723</v>
@@ -7160,10 +7160,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572050</v>
+        <v>572001</v>
       </c>
       <c r="R61" t="n">
-        <v>7078406</v>
+        <v>7078333</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -7225,12 +7225,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7334,7 +7334,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128964127</v>
+        <v>128964698</v>
       </c>
       <c r="B63" t="n">
         <v>92819</v>
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>572008</v>
+        <v>572170</v>
       </c>
       <c r="R63" t="n">
-        <v>7078389</v>
+        <v>7078313</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7429,19 +7429,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128964698</v>
+        <v>128964127</v>
       </c>
       <c r="B64" t="n">
         <v>92819</v>
@@ -7476,10 +7476,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>572170</v>
+        <v>572008</v>
       </c>
       <c r="R64" t="n">
-        <v>7078313</v>
+        <v>7078389</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7536,44 +7536,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128964587</v>
+        <v>128964295</v>
       </c>
       <c r="B65" t="n">
-        <v>90558</v>
+        <v>92819</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7583,10 +7583,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572155</v>
+        <v>572110</v>
       </c>
       <c r="R65" t="n">
-        <v>7078337</v>
+        <v>7078382</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7643,44 +7643,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128964295</v>
+        <v>128964587</v>
       </c>
       <c r="B66" t="n">
-        <v>92819</v>
+        <v>90558</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572110</v>
+        <v>572155</v>
       </c>
       <c r="R66" t="n">
-        <v>7078382</v>
+        <v>7078337</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7750,12 +7750,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -5108,48 +5108,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128963682</v>
+        <v>128968879</v>
       </c>
       <c r="B42" t="n">
-        <v>92823</v>
+        <v>57883</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571916</v>
+        <v>571970</v>
       </c>
       <c r="R42" t="n">
-        <v>7078360</v>
+        <v>7078312</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5176,19 +5176,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5203,60 +5193,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128968879</v>
+        <v>128963682</v>
       </c>
       <c r="B43" t="n">
-        <v>57883</v>
+        <v>92823</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>571970</v>
+        <v>571916</v>
       </c>
       <c r="R43" t="n">
-        <v>7078312</v>
+        <v>7078360</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5283,9 +5273,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5300,12 +5300,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6046,48 +6046,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128967046</v>
+        <v>128968900</v>
       </c>
       <c r="B51" t="n">
-        <v>92835</v>
+        <v>92819</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>571822</v>
+        <v>571998</v>
       </c>
       <c r="R51" t="n">
-        <v>7078359</v>
+        <v>7078374</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6114,19 +6114,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>17:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6141,60 +6131,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128968900</v>
+        <v>128967046</v>
       </c>
       <c r="B52" t="n">
-        <v>92819</v>
+        <v>92835</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>571998</v>
+        <v>571822</v>
       </c>
       <c r="R52" t="n">
-        <v>7078374</v>
+        <v>7078359</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6221,9 +6211,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6238,12 +6238,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -5108,48 +5108,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128968879</v>
+        <v>128963682</v>
       </c>
       <c r="B42" t="n">
-        <v>57883</v>
+        <v>92823</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571970</v>
+        <v>571916</v>
       </c>
       <c r="R42" t="n">
-        <v>7078312</v>
+        <v>7078360</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5176,9 +5176,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5193,60 +5203,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128963682</v>
+        <v>128968879</v>
       </c>
       <c r="B43" t="n">
-        <v>92823</v>
+        <v>57883</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>571916</v>
+        <v>571970</v>
       </c>
       <c r="R43" t="n">
-        <v>7078360</v>
+        <v>7078312</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5273,19 +5283,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5300,60 +5300,65 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128968893</v>
+        <v>128964321</v>
       </c>
       <c r="B44" t="n">
-        <v>92819</v>
+        <v>78701</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571944</v>
+        <v>572123</v>
       </c>
       <c r="R44" t="n">
-        <v>7078352</v>
+        <v>7078382</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5380,9 +5385,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5397,65 +5412,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128964321</v>
+        <v>128968893</v>
       </c>
       <c r="B45" t="n">
-        <v>78701</v>
+        <v>92819</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572123</v>
+        <v>571944</v>
       </c>
       <c r="R45" t="n">
-        <v>7078382</v>
+        <v>7078352</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5482,19 +5492,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5509,12 +5509,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5628,48 +5628,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128963734</v>
+        <v>128968897</v>
       </c>
       <c r="B47" t="n">
-        <v>92813</v>
+        <v>92819</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>571951</v>
+        <v>572106</v>
       </c>
       <c r="R47" t="n">
-        <v>7078394</v>
+        <v>7078370</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5696,19 +5696,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5723,12 +5713,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5842,48 +5832,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128968897</v>
+        <v>128963734</v>
       </c>
       <c r="B49" t="n">
-        <v>92819</v>
+        <v>92813</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572106</v>
+        <v>571951</v>
       </c>
       <c r="R49" t="n">
-        <v>7078370</v>
+        <v>7078394</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5910,9 +5900,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5927,12 +5927,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6250,48 +6250,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128968899</v>
+        <v>128967185</v>
       </c>
       <c r="B53" t="n">
-        <v>92819</v>
+        <v>57723</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572007</v>
+        <v>571833</v>
       </c>
       <c r="R53" t="n">
-        <v>7078343</v>
+        <v>7078283</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6318,9 +6323,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6335,65 +6355,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128967185</v>
+        <v>128968899</v>
       </c>
       <c r="B54" t="n">
-        <v>57723</v>
+        <v>92819</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>571833</v>
+        <v>572007</v>
       </c>
       <c r="R54" t="n">
-        <v>7078283</v>
+        <v>7078343</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6420,24 +6435,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>17:27</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>17:27</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6452,22 +6452,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128963789</v>
+        <v>128964016</v>
       </c>
       <c r="B55" t="n">
-        <v>92813</v>
+        <v>92845</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6475,43 +6475,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>571944</v>
+        <v>572005</v>
       </c>
       <c r="R55" t="n">
-        <v>7078381</v>
+        <v>7078331</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6543,7 +6534,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6553,7 +6544,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6580,10 +6571,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128964016</v>
+        <v>128963789</v>
       </c>
       <c r="B56" t="n">
-        <v>92845</v>
+        <v>92813</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6591,34 +6582,43 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572005</v>
+        <v>571944</v>
       </c>
       <c r="R56" t="n">
-        <v>7078331</v>
+        <v>7078381</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6794,48 +6794,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128967070</v>
+        <v>128968889</v>
       </c>
       <c r="B58" t="n">
-        <v>92819</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>571779</v>
+        <v>572173</v>
       </c>
       <c r="R58" t="n">
-        <v>7078375</v>
+        <v>7078310</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6862,19 +6862,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>17:24</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6889,22 +6884,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128968889</v>
+        <v>128964140</v>
       </c>
       <c r="B59" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6912,37 +6907,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572173</v>
+        <v>572050</v>
       </c>
       <c r="R59" t="n">
-        <v>7078310</v>
+        <v>7078406</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6969,14 +6969,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6991,19 +7001,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128964140</v>
+        <v>128963996</v>
       </c>
       <c r="B60" t="n">
         <v>57723</v>
@@ -7043,10 +7053,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572050</v>
+        <v>572001</v>
       </c>
       <c r="R60" t="n">
-        <v>7078406</v>
+        <v>7078333</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7078,7 +7088,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7088,7 +7098,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7108,62 +7118,57 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128963996</v>
+        <v>128967070</v>
       </c>
       <c r="B61" t="n">
-        <v>57723</v>
+        <v>92819</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572001</v>
+        <v>571779</v>
       </c>
       <c r="R61" t="n">
-        <v>7078333</v>
+        <v>7078375</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7195,7 +7200,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7205,12 +7210,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7225,12 +7225,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7548,45 +7548,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128964295</v>
+        <v>128964634</v>
       </c>
       <c r="B65" t="n">
-        <v>92819</v>
+        <v>57723</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572110</v>
+        <v>572167</v>
       </c>
       <c r="R65" t="n">
-        <v>7078382</v>
+        <v>7078321</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7618,7 +7623,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7628,7 +7633,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7643,12 +7653,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7762,32 +7772,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128964712</v>
+        <v>128964295</v>
       </c>
       <c r="B67" t="n">
-        <v>79035</v>
+        <v>92819</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7797,10 +7807,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572171</v>
+        <v>572110</v>
       </c>
       <c r="R67" t="n">
-        <v>7078312</v>
+        <v>7078382</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7832,7 +7842,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7842,7 +7852,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7869,10 +7879,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128964634</v>
+        <v>128964712</v>
       </c>
       <c r="B68" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7880,39 +7890,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>572167</v>
+        <v>572171</v>
       </c>
       <c r="R68" t="n">
-        <v>7078321</v>
+        <v>7078312</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7944,7 +7949,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7954,12 +7959,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7974,12 +7974,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -4576,7 +4576,7 @@
         <v>128964493</v>
       </c>
       <c r="B37" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>128964288</v>
       </c>
       <c r="B38" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>128964085</v>
       </c>
       <c r="B39" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>128968891</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>128964559</v>
       </c>
       <c r="B41" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>128963682</v>
       </c>
       <c r="B42" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>128968879</v>
       </c>
       <c r="B43" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5312,53 +5312,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128964321</v>
+        <v>128968893</v>
       </c>
       <c r="B44" t="n">
-        <v>78701</v>
+        <v>92826</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572123</v>
+        <v>571944</v>
       </c>
       <c r="R44" t="n">
-        <v>7078382</v>
+        <v>7078352</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5385,19 +5380,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5412,60 +5397,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128968893</v>
+        <v>128964321</v>
       </c>
       <c r="B45" t="n">
-        <v>92819</v>
+        <v>78705</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571944</v>
+        <v>572123</v>
       </c>
       <c r="R45" t="n">
-        <v>7078352</v>
+        <v>7078382</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5492,9 +5482,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5509,12 +5509,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5524,7 +5524,7 @@
         <v>128963835</v>
       </c>
       <c r="B46" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>128968897</v>
       </c>
       <c r="B47" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5725,32 +5725,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128964635</v>
+        <v>128963734</v>
       </c>
       <c r="B48" t="n">
-        <v>92819</v>
+        <v>92820</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5760,10 +5760,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572167</v>
+        <v>571951</v>
       </c>
       <c r="R48" t="n">
-        <v>7078311</v>
+        <v>7078394</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5832,32 +5832,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128963734</v>
+        <v>128964635</v>
       </c>
       <c r="B49" t="n">
-        <v>92813</v>
+        <v>92826</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>571951</v>
+        <v>572167</v>
       </c>
       <c r="R49" t="n">
-        <v>7078394</v>
+        <v>7078311</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5942,7 +5942,7 @@
         <v>128963876</v>
       </c>
       <c r="B50" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>128968900</v>
       </c>
       <c r="B51" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>128967046</v>
       </c>
       <c r="B52" t="n">
-        <v>92835</v>
+        <v>92842</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6250,53 +6250,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128967185</v>
+        <v>128968899</v>
       </c>
       <c r="B53" t="n">
-        <v>57723</v>
+        <v>92826</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>571833</v>
+        <v>572007</v>
       </c>
       <c r="R53" t="n">
-        <v>7078283</v>
+        <v>7078343</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6323,24 +6318,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>17:27</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>17:27</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6355,60 +6335,65 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128968899</v>
+        <v>128967185</v>
       </c>
       <c r="B54" t="n">
-        <v>92819</v>
+        <v>57725</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572007</v>
+        <v>571833</v>
       </c>
       <c r="R54" t="n">
-        <v>7078343</v>
+        <v>7078283</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6435,9 +6420,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6452,22 +6452,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128964016</v>
+        <v>128963789</v>
       </c>
       <c r="B55" t="n">
-        <v>92845</v>
+        <v>92820</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6475,34 +6475,43 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572005</v>
+        <v>571944</v>
       </c>
       <c r="R55" t="n">
-        <v>7078331</v>
+        <v>7078381</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6534,7 +6543,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6544,7 +6553,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6571,10 +6580,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128963789</v>
+        <v>128964016</v>
       </c>
       <c r="B56" t="n">
-        <v>92813</v>
+        <v>92852</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6582,43 +6591,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>571944</v>
+        <v>572005</v>
       </c>
       <c r="R56" t="n">
-        <v>7078381</v>
+        <v>7078331</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6690,7 +6690,7 @@
         <v>128964488</v>
       </c>
       <c r="B57" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6794,48 +6794,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128968889</v>
+        <v>128967070</v>
       </c>
       <c r="B58" t="n">
-        <v>79035</v>
+        <v>92826</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572173</v>
+        <v>571779</v>
       </c>
       <c r="R58" t="n">
-        <v>7078310</v>
+        <v>7078375</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6862,14 +6862,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6884,22 +6889,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128964140</v>
+        <v>128968889</v>
       </c>
       <c r="B59" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6907,42 +6912,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572050</v>
+        <v>572173</v>
       </c>
       <c r="R59" t="n">
-        <v>7078406</v>
+        <v>7078310</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6969,24 +6969,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7001,22 +6991,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128963996</v>
+        <v>128964140</v>
       </c>
       <c r="B60" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7053,10 +7043,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572001</v>
+        <v>572050</v>
       </c>
       <c r="R60" t="n">
-        <v>7078333</v>
+        <v>7078406</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7088,7 +7078,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7098,7 +7088,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7118,57 +7108,62 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128967070</v>
+        <v>128963996</v>
       </c>
       <c r="B61" t="n">
-        <v>92819</v>
+        <v>57725</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>571779</v>
+        <v>572001</v>
       </c>
       <c r="R61" t="n">
-        <v>7078375</v>
+        <v>7078333</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7200,7 +7195,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7210,7 +7205,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7225,12 +7225,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7240,7 +7240,7 @@
         <v>128968898</v>
       </c>
       <c r="B62" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7334,10 +7334,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128964698</v>
+        <v>128964127</v>
       </c>
       <c r="B63" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>572170</v>
+        <v>572008</v>
       </c>
       <c r="R63" t="n">
-        <v>7078313</v>
+        <v>7078389</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7429,22 +7429,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128964127</v>
+        <v>128964698</v>
       </c>
       <c r="B64" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7476,10 +7476,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>572008</v>
+        <v>572170</v>
       </c>
       <c r="R64" t="n">
-        <v>7078389</v>
+        <v>7078313</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7536,22 +7536,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128964634</v>
+        <v>128964712</v>
       </c>
       <c r="B65" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7559,39 +7559,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572167</v>
+        <v>572171</v>
       </c>
       <c r="R65" t="n">
-        <v>7078321</v>
+        <v>7078312</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7623,7 +7618,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7633,12 +7628,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7653,22 +7643,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128964587</v>
+        <v>128964634</v>
       </c>
       <c r="B66" t="n">
-        <v>90558</v>
+        <v>57725</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7676,34 +7666,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572155</v>
+        <v>572167</v>
       </c>
       <c r="R66" t="n">
-        <v>7078337</v>
+        <v>7078321</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7735,7 +7730,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7745,7 +7740,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7775,7 +7775,7 @@
         <v>128964295</v>
       </c>
       <c r="B67" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7879,10 +7879,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128964712</v>
+        <v>128964587</v>
       </c>
       <c r="B68" t="n">
-        <v>79035</v>
+        <v>90562</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7890,21 +7890,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7914,10 +7914,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>572171</v>
+        <v>572155</v>
       </c>
       <c r="R68" t="n">
-        <v>7078312</v>
+        <v>7078337</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7974,12 +7974,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7989,7 +7989,7 @@
         <v>128968892</v>
       </c>
       <c r="B69" t="n">
-        <v>96148</v>
+        <v>96158</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -7548,10 +7548,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128964712</v>
+        <v>128964587</v>
       </c>
       <c r="B65" t="n">
-        <v>79039</v>
+        <v>90562</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7559,21 +7559,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7583,10 +7583,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572171</v>
+        <v>572155</v>
       </c>
       <c r="R65" t="n">
-        <v>7078312</v>
+        <v>7078337</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7643,12 +7643,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7879,10 +7879,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128964587</v>
+        <v>128964712</v>
       </c>
       <c r="B68" t="n">
-        <v>90562</v>
+        <v>79039</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7890,21 +7890,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7914,10 +7914,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>572155</v>
+        <v>572171</v>
       </c>
       <c r="R68" t="n">
-        <v>7078337</v>
+        <v>7078312</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7974,12 +7974,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -4573,10 +4573,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128964493</v>
+        <v>128964288</v>
       </c>
       <c r="B37" t="n">
-        <v>79658</v>
+        <v>57725</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4584,34 +4584,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572133</v>
+        <v>572121</v>
       </c>
       <c r="R37" t="n">
-        <v>7078367</v>
+        <v>7078371</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4643,7 +4648,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4653,7 +4658,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4680,10 +4690,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128964288</v>
+        <v>128964493</v>
       </c>
       <c r="B38" t="n">
-        <v>57725</v>
+        <v>79658</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4691,39 +4701,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572121</v>
+        <v>572133</v>
       </c>
       <c r="R38" t="n">
-        <v>7078371</v>
+        <v>7078367</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4755,7 +4760,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4765,12 +4770,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4800,7 +4800,7 @@
         <v>128964085</v>
       </c>
       <c r="B39" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>128963682</v>
       </c>
       <c r="B42" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,48 +5312,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128968893</v>
+        <v>128964321</v>
       </c>
       <c r="B44" t="n">
-        <v>92826</v>
+        <v>78705</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571944</v>
+        <v>572123</v>
       </c>
       <c r="R44" t="n">
-        <v>7078352</v>
+        <v>7078382</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5380,9 +5385,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5397,65 +5412,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128964321</v>
+        <v>128968893</v>
       </c>
       <c r="B45" t="n">
-        <v>78705</v>
+        <v>92833</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572123</v>
+        <v>571944</v>
       </c>
       <c r="R45" t="n">
-        <v>7078382</v>
+        <v>7078352</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5482,19 +5492,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5509,12 +5509,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5524,7 +5524,7 @@
         <v>128963835</v>
       </c>
       <c r="B46" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>128968897</v>
       </c>
       <c r="B47" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>128963734</v>
       </c>
       <c r="B48" t="n">
-        <v>92820</v>
+        <v>92827</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>128964635</v>
       </c>
       <c r="B49" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>128963876</v>
       </c>
       <c r="B50" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6046,48 +6046,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128968900</v>
+        <v>128967046</v>
       </c>
       <c r="B51" t="n">
-        <v>92826</v>
+        <v>92849</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>571998</v>
+        <v>571822</v>
       </c>
       <c r="R51" t="n">
-        <v>7078374</v>
+        <v>7078359</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6114,9 +6114,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6131,60 +6141,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128967046</v>
+        <v>128968900</v>
       </c>
       <c r="B52" t="n">
-        <v>92842</v>
+        <v>92833</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>571822</v>
+        <v>571998</v>
       </c>
       <c r="R52" t="n">
-        <v>7078359</v>
+        <v>7078374</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6211,19 +6221,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>17:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6238,12 +6238,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6253,7 +6253,7 @@
         <v>128968899</v>
       </c>
       <c r="B53" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>128963789</v>
       </c>
       <c r="B55" t="n">
-        <v>92820</v>
+        <v>92827</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>128964016</v>
       </c>
       <c r="B56" t="n">
-        <v>92852</v>
+        <v>92859</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>128967070</v>
       </c>
       <c r="B58" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6901,10 +6901,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128968889</v>
+        <v>128963996</v>
       </c>
       <c r="B59" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6912,37 +6912,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572173</v>
+        <v>572001</v>
       </c>
       <c r="R59" t="n">
-        <v>7078310</v>
+        <v>7078333</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6969,14 +6974,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6991,12 +7006,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7120,10 +7135,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128963996</v>
+        <v>128968889</v>
       </c>
       <c r="B61" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7131,42 +7146,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572001</v>
+        <v>572173</v>
       </c>
       <c r="R61" t="n">
-        <v>7078333</v>
+        <v>7078310</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7193,24 +7203,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7225,12 +7225,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7240,7 +7240,7 @@
         <v>128968898</v>
       </c>
       <c r="B62" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>128964127</v>
       </c>
       <c r="B63" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>128964698</v>
       </c>
       <c r="B64" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7548,32 +7548,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128964587</v>
+        <v>128964295</v>
       </c>
       <c r="B65" t="n">
-        <v>90562</v>
+        <v>92833</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7583,10 +7583,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572155</v>
+        <v>572110</v>
       </c>
       <c r="R65" t="n">
-        <v>7078337</v>
+        <v>7078382</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7643,22 +7643,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128964634</v>
+        <v>128964587</v>
       </c>
       <c r="B66" t="n">
-        <v>57725</v>
+        <v>90569</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,39 +7666,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572167</v>
+        <v>572155</v>
       </c>
       <c r="R66" t="n">
-        <v>7078321</v>
+        <v>7078337</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7730,7 +7725,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7740,12 +7735,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7772,32 +7762,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128964295</v>
+        <v>128964712</v>
       </c>
       <c r="B67" t="n">
-        <v>92826</v>
+        <v>79039</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7807,10 +7797,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572110</v>
+        <v>572171</v>
       </c>
       <c r="R67" t="n">
-        <v>7078382</v>
+        <v>7078312</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7842,7 +7832,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7852,7 +7842,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7879,10 +7869,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128964712</v>
+        <v>128964634</v>
       </c>
       <c r="B68" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7890,34 +7880,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>572171</v>
+        <v>572167</v>
       </c>
       <c r="R68" t="n">
-        <v>7078312</v>
+        <v>7078321</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7949,7 +7944,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7959,7 +7954,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7974,12 +7974,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7989,7 +7989,7 @@
         <v>128968892</v>
       </c>
       <c r="B69" t="n">
-        <v>96158</v>
+        <v>96165</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -4573,10 +4573,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128964288</v>
+        <v>128964493</v>
       </c>
       <c r="B37" t="n">
-        <v>57725</v>
+        <v>79660</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4584,39 +4584,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572121</v>
+        <v>572133</v>
       </c>
       <c r="R37" t="n">
-        <v>7078371</v>
+        <v>7078367</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4648,7 +4643,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4658,12 +4653,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4690,10 +4680,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128964493</v>
+        <v>128964288</v>
       </c>
       <c r="B38" t="n">
-        <v>79658</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4701,34 +4691,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572133</v>
+        <v>572121</v>
       </c>
       <c r="R38" t="n">
-        <v>7078367</v>
+        <v>7078371</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4760,7 +4755,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4770,7 +4765,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4800,7 +4800,7 @@
         <v>128964085</v>
       </c>
       <c r="B39" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>128968891</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>128964559</v>
       </c>
       <c r="B41" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5108,48 +5108,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128963682</v>
+        <v>128968879</v>
       </c>
       <c r="B42" t="n">
-        <v>92837</v>
+        <v>57887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571916</v>
+        <v>571970</v>
       </c>
       <c r="R42" t="n">
-        <v>7078360</v>
+        <v>7078312</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5176,19 +5176,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5203,60 +5193,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128968879</v>
+        <v>128963682</v>
       </c>
       <c r="B43" t="n">
-        <v>57885</v>
+        <v>92839</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>571970</v>
+        <v>571916</v>
       </c>
       <c r="R43" t="n">
-        <v>7078312</v>
+        <v>7078360</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5283,9 +5273,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5300,65 +5300,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128964321</v>
+        <v>128968893</v>
       </c>
       <c r="B44" t="n">
-        <v>78705</v>
+        <v>92835</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572123</v>
+        <v>571944</v>
       </c>
       <c r="R44" t="n">
-        <v>7078382</v>
+        <v>7078352</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5385,19 +5380,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5412,60 +5397,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128968893</v>
+        <v>128964321</v>
       </c>
       <c r="B45" t="n">
-        <v>92833</v>
+        <v>78707</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571944</v>
+        <v>572123</v>
       </c>
       <c r="R45" t="n">
-        <v>7078352</v>
+        <v>7078382</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5492,9 +5482,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5509,22 +5509,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128963835</v>
+        <v>128968897</v>
       </c>
       <c r="B46" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5552,17 +5552,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>571961</v>
+        <v>572106</v>
       </c>
       <c r="R46" t="n">
-        <v>7078380</v>
+        <v>7078370</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5589,19 +5589,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5616,22 +5606,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128968897</v>
+        <v>128964635</v>
       </c>
       <c r="B47" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5659,17 +5649,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572106</v>
+        <v>572167</v>
       </c>
       <c r="R47" t="n">
-        <v>7078370</v>
+        <v>7078311</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5696,9 +5686,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5713,44 +5713,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128963734</v>
+        <v>128963835</v>
       </c>
       <c r="B48" t="n">
-        <v>92827</v>
+        <v>92835</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5760,10 +5760,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>571951</v>
+        <v>571961</v>
       </c>
       <c r="R48" t="n">
-        <v>7078394</v>
+        <v>7078380</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5832,32 +5832,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128964635</v>
+        <v>128963734</v>
       </c>
       <c r="B49" t="n">
-        <v>92833</v>
+        <v>92829</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572167</v>
+        <v>571951</v>
       </c>
       <c r="R49" t="n">
-        <v>7078311</v>
+        <v>7078394</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5942,7 +5942,7 @@
         <v>128963876</v>
       </c>
       <c r="B50" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6046,48 +6046,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128967046</v>
+        <v>128968900</v>
       </c>
       <c r="B51" t="n">
-        <v>92849</v>
+        <v>92835</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>571822</v>
+        <v>571998</v>
       </c>
       <c r="R51" t="n">
-        <v>7078359</v>
+        <v>7078374</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6114,19 +6114,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>17:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6141,60 +6131,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128968900</v>
+        <v>128967046</v>
       </c>
       <c r="B52" t="n">
-        <v>92833</v>
+        <v>92851</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>571998</v>
+        <v>571822</v>
       </c>
       <c r="R52" t="n">
-        <v>7078374</v>
+        <v>7078359</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6221,9 +6211,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6238,12 +6238,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6253,7 +6253,7 @@
         <v>128968899</v>
       </c>
       <c r="B53" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>128967185</v>
       </c>
       <c r="B54" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6464,10 +6464,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128963789</v>
+        <v>128964016</v>
       </c>
       <c r="B55" t="n">
-        <v>92827</v>
+        <v>92861</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6475,43 +6475,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>571944</v>
+        <v>572005</v>
       </c>
       <c r="R55" t="n">
-        <v>7078381</v>
+        <v>7078331</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6543,7 +6534,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6553,7 +6544,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6580,10 +6571,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128964016</v>
+        <v>128963789</v>
       </c>
       <c r="B56" t="n">
-        <v>92859</v>
+        <v>92829</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6591,34 +6582,43 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572005</v>
+        <v>571944</v>
       </c>
       <c r="R56" t="n">
-        <v>7078331</v>
+        <v>7078381</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6690,7 +6690,7 @@
         <v>128964488</v>
       </c>
       <c r="B57" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6794,45 +6794,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128967070</v>
+        <v>128964140</v>
       </c>
       <c r="B58" t="n">
-        <v>92833</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>571779</v>
+        <v>572050</v>
       </c>
       <c r="R58" t="n">
-        <v>7078375</v>
+        <v>7078406</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6864,7 +6869,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6874,7 +6879,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6904,7 +6914,7 @@
         <v>128963996</v>
       </c>
       <c r="B59" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7018,50 +7028,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128964140</v>
+        <v>128967070</v>
       </c>
       <c r="B60" t="n">
-        <v>57725</v>
+        <v>92835</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572050</v>
+        <v>571779</v>
       </c>
       <c r="R60" t="n">
-        <v>7078406</v>
+        <v>7078375</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7093,7 +7098,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7103,12 +7108,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7138,7 +7138,7 @@
         <v>128968889</v>
       </c>
       <c r="B61" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>128968898</v>
       </c>
       <c r="B62" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>128964127</v>
       </c>
       <c r="B63" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>128964698</v>
       </c>
       <c r="B64" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>128964295</v>
       </c>
       <c r="B65" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7655,10 +7655,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128964587</v>
+        <v>128964712</v>
       </c>
       <c r="B66" t="n">
-        <v>90569</v>
+        <v>79041</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,21 +7666,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572155</v>
+        <v>572171</v>
       </c>
       <c r="R66" t="n">
-        <v>7078337</v>
+        <v>7078312</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7750,22 +7750,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128964712</v>
+        <v>128964587</v>
       </c>
       <c r="B67" t="n">
-        <v>79039</v>
+        <v>90571</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7773,21 +7773,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572171</v>
+        <v>572155</v>
       </c>
       <c r="R67" t="n">
-        <v>7078312</v>
+        <v>7078337</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7857,12 +7857,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7872,7 +7872,7 @@
         <v>128964634</v>
       </c>
       <c r="B68" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>128968892</v>
       </c>
       <c r="B69" t="n">
-        <v>96165</v>
+        <v>96167</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5108,48 +5108,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128968879</v>
+        <v>128963682</v>
       </c>
       <c r="B42" t="n">
-        <v>57887</v>
+        <v>92839</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571970</v>
+        <v>571916</v>
       </c>
       <c r="R42" t="n">
-        <v>7078312</v>
+        <v>7078360</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5176,9 +5176,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5193,60 +5203,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128963682</v>
+        <v>128968879</v>
       </c>
       <c r="B43" t="n">
-        <v>92839</v>
+        <v>57887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>571916</v>
+        <v>571970</v>
       </c>
       <c r="R43" t="n">
-        <v>7078360</v>
+        <v>7078312</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5273,19 +5283,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5300,12 +5300,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5521,7 +5521,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128968897</v>
+        <v>128963835</v>
       </c>
       <c r="B46" t="n">
         <v>92835</v>
@@ -5552,17 +5552,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572106</v>
+        <v>571961</v>
       </c>
       <c r="R46" t="n">
-        <v>7078370</v>
+        <v>7078380</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5589,9 +5589,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5606,19 +5616,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128964635</v>
+        <v>128968897</v>
       </c>
       <c r="B47" t="n">
         <v>92835</v>
@@ -5649,17 +5659,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572167</v>
+        <v>572106</v>
       </c>
       <c r="R47" t="n">
-        <v>7078311</v>
+        <v>7078370</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5686,19 +5696,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5713,19 +5713,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128963835</v>
+        <v>128964635</v>
       </c>
       <c r="B48" t="n">
         <v>92835</v>
@@ -5760,10 +5760,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>571961</v>
+        <v>572167</v>
       </c>
       <c r="R48" t="n">
-        <v>7078380</v>
+        <v>7078311</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6046,48 +6046,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128968900</v>
+        <v>128967046</v>
       </c>
       <c r="B51" t="n">
-        <v>92835</v>
+        <v>92851</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>571998</v>
+        <v>571822</v>
       </c>
       <c r="R51" t="n">
-        <v>7078374</v>
+        <v>7078359</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6114,9 +6114,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6131,60 +6141,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128967046</v>
+        <v>128968900</v>
       </c>
       <c r="B52" t="n">
-        <v>92851</v>
+        <v>92835</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>571822</v>
+        <v>571998</v>
       </c>
       <c r="R52" t="n">
-        <v>7078359</v>
+        <v>7078374</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6211,19 +6221,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>17:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6238,12 +6238,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6464,10 +6464,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128964016</v>
+        <v>128963789</v>
       </c>
       <c r="B55" t="n">
-        <v>92861</v>
+        <v>92829</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6475,34 +6475,43 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572005</v>
+        <v>571944</v>
       </c>
       <c r="R55" t="n">
-        <v>7078331</v>
+        <v>7078381</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6534,7 +6543,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6544,7 +6553,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6571,10 +6580,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128963789</v>
+        <v>128964488</v>
       </c>
       <c r="B56" t="n">
-        <v>92829</v>
+        <v>78798</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6582,43 +6591,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>571944</v>
+        <v>572134</v>
       </c>
       <c r="R56" t="n">
-        <v>7078381</v>
+        <v>7078366</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6687,10 +6687,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128964488</v>
+        <v>128964016</v>
       </c>
       <c r="B57" t="n">
-        <v>78798</v>
+        <v>92861</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6698,21 +6698,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>5448</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6722,10 +6722,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572134</v>
+        <v>572005</v>
       </c>
       <c r="R57" t="n">
-        <v>7078366</v>
+        <v>7078331</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6794,50 +6794,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128964140</v>
+        <v>128967070</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>92835</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572050</v>
+        <v>571779</v>
       </c>
       <c r="R58" t="n">
-        <v>7078406</v>
+        <v>7078375</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6869,7 +6864,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6879,12 +6874,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6911,10 +6901,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128963996</v>
+        <v>128968889</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6922,42 +6912,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572001</v>
+        <v>572173</v>
       </c>
       <c r="R59" t="n">
-        <v>7078333</v>
+        <v>7078310</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6984,24 +6969,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7016,57 +6991,62 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128967070</v>
+        <v>128963996</v>
       </c>
       <c r="B60" t="n">
-        <v>92835</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>571779</v>
+        <v>572001</v>
       </c>
       <c r="R60" t="n">
-        <v>7078375</v>
+        <v>7078333</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7098,7 +7078,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7108,7 +7088,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7123,22 +7108,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128968889</v>
+        <v>128964140</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7146,37 +7131,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572173</v>
+        <v>572050</v>
       </c>
       <c r="R61" t="n">
-        <v>7078310</v>
+        <v>7078406</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7203,14 +7193,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7225,12 +7225,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7655,10 +7655,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128964712</v>
+        <v>128964587</v>
       </c>
       <c r="B66" t="n">
-        <v>79041</v>
+        <v>90571</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,21 +7666,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572171</v>
+        <v>572155</v>
       </c>
       <c r="R66" t="n">
-        <v>7078312</v>
+        <v>7078337</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7750,22 +7750,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128964587</v>
+        <v>128964712</v>
       </c>
       <c r="B67" t="n">
-        <v>90571</v>
+        <v>79041</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7773,21 +7773,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572155</v>
+        <v>572171</v>
       </c>
       <c r="R67" t="n">
-        <v>7078337</v>
+        <v>7078312</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7857,12 +7857,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8081,6 +8081,418 @@
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129341563</v>
+      </c>
+      <c r="B70" t="n">
+        <v>90571</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>571920</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7078320</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129340276</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91949</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>572157</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7078330</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129337812</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91703</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>571918</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7078355</v>
+      </c>
+      <c r="S72" t="n">
+        <v>15</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129341362</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>571975</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7078298</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -4573,10 +4573,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128964493</v>
+        <v>128964288</v>
       </c>
       <c r="B37" t="n">
-        <v>79660</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4584,34 +4584,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572133</v>
+        <v>572121</v>
       </c>
       <c r="R37" t="n">
-        <v>7078367</v>
+        <v>7078371</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4643,7 +4648,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4653,7 +4658,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4680,10 +4690,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128964288</v>
+        <v>128964493</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>79660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4691,39 +4701,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572121</v>
+        <v>572133</v>
       </c>
       <c r="R38" t="n">
-        <v>7078371</v>
+        <v>7078367</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4755,7 +4760,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4765,12 +4770,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5312,48 +5312,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128968893</v>
+        <v>128964321</v>
       </c>
       <c r="B44" t="n">
-        <v>92835</v>
+        <v>78707</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571944</v>
+        <v>572123</v>
       </c>
       <c r="R44" t="n">
-        <v>7078352</v>
+        <v>7078382</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5380,9 +5385,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5397,65 +5412,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128964321</v>
+        <v>128968893</v>
       </c>
       <c r="B45" t="n">
-        <v>78707</v>
+        <v>92835</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572123</v>
+        <v>571944</v>
       </c>
       <c r="R45" t="n">
-        <v>7078382</v>
+        <v>7078352</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5482,19 +5492,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5509,12 +5509,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -7548,32 +7548,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128964295</v>
+        <v>128964587</v>
       </c>
       <c r="B65" t="n">
-        <v>92835</v>
+        <v>90571</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7583,10 +7583,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572110</v>
+        <v>572155</v>
       </c>
       <c r="R65" t="n">
-        <v>7078382</v>
+        <v>7078337</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7643,22 +7643,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128964587</v>
+        <v>128964712</v>
       </c>
       <c r="B66" t="n">
-        <v>90571</v>
+        <v>79041</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,21 +7666,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572155</v>
+        <v>572171</v>
       </c>
       <c r="R66" t="n">
-        <v>7078337</v>
+        <v>7078312</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7750,22 +7750,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128964712</v>
+        <v>128964634</v>
       </c>
       <c r="B67" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7773,34 +7773,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572171</v>
+        <v>572167</v>
       </c>
       <c r="R67" t="n">
-        <v>7078312</v>
+        <v>7078321</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7832,7 +7837,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7842,7 +7847,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7857,62 +7867,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128964634</v>
+        <v>128964295</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>92835</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>572167</v>
+        <v>572110</v>
       </c>
       <c r="R68" t="n">
-        <v>7078321</v>
+        <v>7078382</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7944,7 +7949,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7954,12 +7959,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7974,12 +7974,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -4800,7 +4800,7 @@
         <v>128964085</v>
       </c>
       <c r="B39" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>128963682</v>
       </c>
       <c r="B42" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,53 +5312,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128964321</v>
+        <v>128968893</v>
       </c>
       <c r="B44" t="n">
-        <v>78707</v>
+        <v>92821</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572123</v>
+        <v>571944</v>
       </c>
       <c r="R44" t="n">
-        <v>7078382</v>
+        <v>7078352</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5385,19 +5380,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5412,60 +5397,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128968893</v>
+        <v>128964321</v>
       </c>
       <c r="B45" t="n">
-        <v>92835</v>
+        <v>78707</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571944</v>
+        <v>572123</v>
       </c>
       <c r="R45" t="n">
-        <v>7078352</v>
+        <v>7078382</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5492,9 +5482,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5509,12 +5509,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5524,7 +5524,7 @@
         <v>128963835</v>
       </c>
       <c r="B46" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>128968897</v>
       </c>
       <c r="B47" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5725,32 +5725,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128964635</v>
+        <v>128963734</v>
       </c>
       <c r="B48" t="n">
-        <v>92835</v>
+        <v>92815</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5760,10 +5760,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572167</v>
+        <v>571951</v>
       </c>
       <c r="R48" t="n">
-        <v>7078311</v>
+        <v>7078394</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5832,32 +5832,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128963734</v>
+        <v>128964635</v>
       </c>
       <c r="B49" t="n">
-        <v>92829</v>
+        <v>92821</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>571951</v>
+        <v>572167</v>
       </c>
       <c r="R49" t="n">
-        <v>7078394</v>
+        <v>7078311</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5942,7 +5942,7 @@
         <v>128963876</v>
       </c>
       <c r="B50" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>128967046</v>
       </c>
       <c r="B51" t="n">
-        <v>92851</v>
+        <v>92837</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>128968900</v>
       </c>
       <c r="B52" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>128968899</v>
       </c>
       <c r="B53" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6464,10 +6464,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128963789</v>
+        <v>128964488</v>
       </c>
       <c r="B55" t="n">
-        <v>92829</v>
+        <v>78798</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6475,43 +6475,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>571944</v>
+        <v>572134</v>
       </c>
       <c r="R55" t="n">
-        <v>7078381</v>
+        <v>7078366</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6543,7 +6534,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6553,7 +6544,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6580,10 +6571,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128964488</v>
+        <v>128963789</v>
       </c>
       <c r="B56" t="n">
-        <v>78798</v>
+        <v>92815</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6591,34 +6582,43 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572134</v>
+        <v>571944</v>
       </c>
       <c r="R56" t="n">
-        <v>7078366</v>
+        <v>7078381</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6690,7 +6690,7 @@
         <v>128964016</v>
       </c>
       <c r="B57" t="n">
-        <v>92861</v>
+        <v>92847</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>128967070</v>
       </c>
       <c r="B58" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128963996</v>
+        <v>128964140</v>
       </c>
       <c r="B60" t="n">
         <v>57727</v>
@@ -7043,10 +7043,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572001</v>
+        <v>572050</v>
       </c>
       <c r="R60" t="n">
-        <v>7078333</v>
+        <v>7078406</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7108,19 +7108,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128964140</v>
+        <v>128963996</v>
       </c>
       <c r="B61" t="n">
         <v>57727</v>
@@ -7160,10 +7160,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572050</v>
+        <v>572001</v>
       </c>
       <c r="R61" t="n">
-        <v>7078406</v>
+        <v>7078333</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -7225,12 +7225,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7240,7 +7240,7 @@
         <v>128968898</v>
       </c>
       <c r="B62" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>128964127</v>
       </c>
       <c r="B63" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>128964698</v>
       </c>
       <c r="B64" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7548,32 +7548,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128964587</v>
+        <v>128964295</v>
       </c>
       <c r="B65" t="n">
-        <v>90571</v>
+        <v>92821</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7583,10 +7583,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572155</v>
+        <v>572110</v>
       </c>
       <c r="R65" t="n">
-        <v>7078337</v>
+        <v>7078382</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7643,12 +7643,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7879,32 +7879,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128964295</v>
+        <v>128964587</v>
       </c>
       <c r="B68" t="n">
-        <v>92835</v>
+        <v>90572</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7914,10 +7914,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>572110</v>
+        <v>572155</v>
       </c>
       <c r="R68" t="n">
-        <v>7078382</v>
+        <v>7078337</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7974,12 +7974,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7989,7 +7989,7 @@
         <v>128968892</v>
       </c>
       <c r="B69" t="n">
-        <v>96167</v>
+        <v>96193</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>129341563</v>
       </c>
       <c r="B70" t="n">
-        <v>90571</v>
+        <v>90572</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>129340276</v>
       </c>
       <c r="B71" t="n">
-        <v>91949</v>
+        <v>91957</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8291,45 +8291,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129337812</v>
+        <v>129341362</v>
       </c>
       <c r="B72" t="n">
-        <v>91703</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>571918</v>
+        <v>571975</v>
       </c>
       <c r="R72" t="n">
-        <v>7078355</v>
+        <v>7078298</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8362,6 +8367,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8388,50 +8398,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129341362</v>
+        <v>129337812</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>91712</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>571975</v>
+        <v>571918</v>
       </c>
       <c r="R73" t="n">
-        <v>7078298</v>
+        <v>7078355</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8464,11 +8469,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4573,10 +4573,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128964288</v>
+        <v>128964493</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>79660</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4584,39 +4584,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572121</v>
+        <v>572133</v>
       </c>
       <c r="R37" t="n">
-        <v>7078371</v>
+        <v>7078367</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4648,7 +4643,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4658,12 +4653,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4690,10 +4680,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128964493</v>
+        <v>128964288</v>
       </c>
       <c r="B38" t="n">
-        <v>79660</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4701,34 +4691,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572133</v>
+        <v>572121</v>
       </c>
       <c r="R38" t="n">
-        <v>7078367</v>
+        <v>7078371</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4760,7 +4755,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4770,7 +4765,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4800,7 +4800,7 @@
         <v>128964085</v>
       </c>
       <c r="B39" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>128963682</v>
       </c>
       <c r="B42" t="n">
-        <v>92825</v>
+        <v>92826</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>128968893</v>
       </c>
       <c r="B44" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5521,10 +5521,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128963835</v>
+        <v>128968897</v>
       </c>
       <c r="B46" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5552,17 +5552,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>571961</v>
+        <v>572106</v>
       </c>
       <c r="R46" t="n">
-        <v>7078380</v>
+        <v>7078370</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5589,19 +5589,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5616,22 +5606,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128968897</v>
+        <v>128964635</v>
       </c>
       <c r="B47" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5659,17 +5649,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572106</v>
+        <v>572167</v>
       </c>
       <c r="R47" t="n">
-        <v>7078370</v>
+        <v>7078311</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5696,9 +5686,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5713,44 +5713,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128963734</v>
+        <v>128963835</v>
       </c>
       <c r="B48" t="n">
-        <v>92815</v>
+        <v>92822</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5760,10 +5760,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>571951</v>
+        <v>571961</v>
       </c>
       <c r="R48" t="n">
-        <v>7078394</v>
+        <v>7078380</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5832,32 +5832,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128964635</v>
+        <v>128963734</v>
       </c>
       <c r="B49" t="n">
-        <v>92821</v>
+        <v>92816</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572167</v>
+        <v>571951</v>
       </c>
       <c r="R49" t="n">
-        <v>7078311</v>
+        <v>7078394</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5942,7 +5942,7 @@
         <v>128963876</v>
       </c>
       <c r="B50" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>128967046</v>
       </c>
       <c r="B51" t="n">
-        <v>92837</v>
+        <v>92838</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>128968900</v>
       </c>
       <c r="B52" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6250,48 +6250,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128968899</v>
+        <v>128967185</v>
       </c>
       <c r="B53" t="n">
-        <v>92821</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572007</v>
+        <v>571833</v>
       </c>
       <c r="R53" t="n">
-        <v>7078343</v>
+        <v>7078283</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6318,9 +6323,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6335,65 +6355,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128967185</v>
+        <v>128968899</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>92822</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>571833</v>
+        <v>572007</v>
       </c>
       <c r="R54" t="n">
-        <v>7078283</v>
+        <v>7078343</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6420,24 +6435,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>17:27</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>17:27</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6452,22 +6452,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128964488</v>
+        <v>128964016</v>
       </c>
       <c r="B55" t="n">
-        <v>78798</v>
+        <v>92848</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6475,21 +6475,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>5448</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572134</v>
+        <v>572005</v>
       </c>
       <c r="R55" t="n">
-        <v>7078366</v>
+        <v>7078331</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6574,7 +6574,7 @@
         <v>128963789</v>
       </c>
       <c r="B56" t="n">
-        <v>92815</v>
+        <v>92816</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6687,10 +6687,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128964016</v>
+        <v>128964488</v>
       </c>
       <c r="B57" t="n">
-        <v>92847</v>
+        <v>78798</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6698,21 +6698,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5448</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6722,10 +6722,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572005</v>
+        <v>572134</v>
       </c>
       <c r="R57" t="n">
-        <v>7078331</v>
+        <v>7078366</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6794,48 +6794,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128967070</v>
+        <v>128968889</v>
       </c>
       <c r="B58" t="n">
-        <v>92821</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>571779</v>
+        <v>572173</v>
       </c>
       <c r="R58" t="n">
-        <v>7078375</v>
+        <v>7078310</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6862,19 +6862,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>17:24</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6889,22 +6884,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128968889</v>
+        <v>128964140</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6912,37 +6907,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572173</v>
+        <v>572050</v>
       </c>
       <c r="R59" t="n">
-        <v>7078310</v>
+        <v>7078406</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6969,14 +6969,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6991,19 +7001,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128964140</v>
+        <v>128963996</v>
       </c>
       <c r="B60" t="n">
         <v>57727</v>
@@ -7043,10 +7053,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572050</v>
+        <v>572001</v>
       </c>
       <c r="R60" t="n">
-        <v>7078406</v>
+        <v>7078333</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7078,7 +7088,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7088,7 +7098,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7108,62 +7118,57 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128963996</v>
+        <v>128967070</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>92822</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572001</v>
+        <v>571779</v>
       </c>
       <c r="R61" t="n">
-        <v>7078333</v>
+        <v>7078375</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7195,7 +7200,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7205,12 +7210,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7225,12 +7225,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7240,7 +7240,7 @@
         <v>128968898</v>
       </c>
       <c r="B62" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>128964127</v>
       </c>
       <c r="B63" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>128964698</v>
       </c>
       <c r="B64" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7548,45 +7548,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128964295</v>
+        <v>128964634</v>
       </c>
       <c r="B65" t="n">
-        <v>92821</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572110</v>
+        <v>572167</v>
       </c>
       <c r="R65" t="n">
-        <v>7078382</v>
+        <v>7078321</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7618,7 +7623,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7628,7 +7633,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7643,12 +7653,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7762,50 +7772,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128964634</v>
+        <v>128964295</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>92822</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572167</v>
+        <v>572110</v>
       </c>
       <c r="R67" t="n">
-        <v>7078321</v>
+        <v>7078382</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7837,7 +7842,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7847,12 +7852,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7867,12 +7867,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7989,7 +7989,7 @@
         <v>128968892</v>
       </c>
       <c r="B69" t="n">
-        <v>96193</v>
+        <v>96194</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>129340276</v>
       </c>
       <c r="B71" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8291,50 +8291,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129341362</v>
+        <v>129337812</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>91713</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>571975</v>
+        <v>571918</v>
       </c>
       <c r="R72" t="n">
-        <v>7078298</v>
+        <v>7078355</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8367,11 +8362,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8398,45 +8388,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129337812</v>
+        <v>129341362</v>
       </c>
       <c r="B73" t="n">
-        <v>91712</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>571918</v>
+        <v>571975</v>
       </c>
       <c r="R73" t="n">
-        <v>7078355</v>
+        <v>7078298</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8471,6 +8466,11 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -8492,6 +8492,122 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129403423</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57831</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>572086</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7078399</v>
+      </c>
+      <c r="S74" t="n">
+        <v>20</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -5312,48 +5312,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128968893</v>
+        <v>128964321</v>
       </c>
       <c r="B44" t="n">
-        <v>92822</v>
+        <v>78707</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571944</v>
+        <v>572123</v>
       </c>
       <c r="R44" t="n">
-        <v>7078352</v>
+        <v>7078382</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5380,9 +5385,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5397,65 +5412,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128964321</v>
+        <v>128968893</v>
       </c>
       <c r="B45" t="n">
-        <v>78707</v>
+        <v>92822</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572123</v>
+        <v>571944</v>
       </c>
       <c r="R45" t="n">
-        <v>7078382</v>
+        <v>7078352</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5482,19 +5492,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5509,19 +5509,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128968897</v>
+        <v>128963835</v>
       </c>
       <c r="B46" t="n">
         <v>92822</v>
@@ -5552,17 +5552,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572106</v>
+        <v>571961</v>
       </c>
       <c r="R46" t="n">
-        <v>7078370</v>
+        <v>7078380</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5589,9 +5589,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5606,19 +5616,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128964635</v>
+        <v>128968897</v>
       </c>
       <c r="B47" t="n">
         <v>92822</v>
@@ -5649,17 +5659,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572167</v>
+        <v>572106</v>
       </c>
       <c r="R47" t="n">
-        <v>7078311</v>
+        <v>7078370</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5686,19 +5696,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5713,44 +5713,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128963835</v>
+        <v>128963734</v>
       </c>
       <c r="B48" t="n">
-        <v>92822</v>
+        <v>92816</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5760,10 +5760,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>571961</v>
+        <v>571951</v>
       </c>
       <c r="R48" t="n">
-        <v>7078380</v>
+        <v>7078394</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5832,32 +5832,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128963734</v>
+        <v>128964635</v>
       </c>
       <c r="B49" t="n">
-        <v>92816</v>
+        <v>92822</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>571951</v>
+        <v>572167</v>
       </c>
       <c r="R49" t="n">
-        <v>7078394</v>
+        <v>7078311</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6250,53 +6250,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128967185</v>
+        <v>128968899</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>92822</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>571833</v>
+        <v>572007</v>
       </c>
       <c r="R53" t="n">
-        <v>7078283</v>
+        <v>7078343</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6323,24 +6318,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>17:27</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>17:27</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6355,60 +6335,65 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128968899</v>
+        <v>128967185</v>
       </c>
       <c r="B54" t="n">
-        <v>92822</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572007</v>
+        <v>571833</v>
       </c>
       <c r="R54" t="n">
-        <v>7078343</v>
+        <v>7078283</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6435,9 +6420,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6452,22 +6452,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128964016</v>
+        <v>128964488</v>
       </c>
       <c r="B55" t="n">
-        <v>92848</v>
+        <v>78798</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6475,21 +6475,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5448</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572005</v>
+        <v>572134</v>
       </c>
       <c r="R55" t="n">
-        <v>7078331</v>
+        <v>7078366</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6571,10 +6571,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128963789</v>
+        <v>128964016</v>
       </c>
       <c r="B56" t="n">
-        <v>92816</v>
+        <v>92848</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6582,43 +6582,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>571944</v>
+        <v>572005</v>
       </c>
       <c r="R56" t="n">
-        <v>7078381</v>
+        <v>7078331</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6650,7 +6641,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6660,7 +6651,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6687,10 +6678,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128964488</v>
+        <v>128963789</v>
       </c>
       <c r="B57" t="n">
-        <v>78798</v>
+        <v>92816</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6698,34 +6689,43 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572134</v>
+        <v>571944</v>
       </c>
       <c r="R57" t="n">
-        <v>7078366</v>
+        <v>7078381</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6794,10 +6794,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128968889</v>
+        <v>128964140</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6805,37 +6805,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572173</v>
+        <v>572050</v>
       </c>
       <c r="R58" t="n">
-        <v>7078310</v>
+        <v>7078406</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6862,14 +6867,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6884,19 +6899,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128964140</v>
+        <v>128963996</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -6936,10 +6951,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572050</v>
+        <v>572001</v>
       </c>
       <c r="R59" t="n">
-        <v>7078406</v>
+        <v>7078333</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6971,7 +6986,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6981,7 +6996,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -7001,62 +7016,57 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128963996</v>
+        <v>128967070</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>92822</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572001</v>
+        <v>571779</v>
       </c>
       <c r="R60" t="n">
-        <v>7078333</v>
+        <v>7078375</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7088,7 +7098,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7098,12 +7108,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7118,60 +7123,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128967070</v>
+        <v>128968889</v>
       </c>
       <c r="B61" t="n">
-        <v>92822</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>571779</v>
+        <v>572173</v>
       </c>
       <c r="R61" t="n">
-        <v>7078375</v>
+        <v>7078310</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7198,19 +7203,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>17:24</t>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7225,12 +7225,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7548,10 +7548,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128964634</v>
+        <v>128964587</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>90572</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7559,39 +7559,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572167</v>
+        <v>572155</v>
       </c>
       <c r="R65" t="n">
-        <v>7078321</v>
+        <v>7078337</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7623,7 +7618,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7633,12 +7628,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7665,32 +7655,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128964712</v>
+        <v>128964295</v>
       </c>
       <c r="B66" t="n">
-        <v>79041</v>
+        <v>92822</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7700,10 +7690,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572171</v>
+        <v>572110</v>
       </c>
       <c r="R66" t="n">
-        <v>7078312</v>
+        <v>7078382</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7735,7 +7725,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7745,7 +7735,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7772,32 +7762,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128964295</v>
+        <v>128964712</v>
       </c>
       <c r="B67" t="n">
-        <v>92822</v>
+        <v>79041</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7807,10 +7797,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572110</v>
+        <v>572171</v>
       </c>
       <c r="R67" t="n">
-        <v>7078382</v>
+        <v>7078312</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7842,7 +7832,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7852,7 +7842,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7879,10 +7869,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128964587</v>
+        <v>128964634</v>
       </c>
       <c r="B68" t="n">
-        <v>90572</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7890,34 +7880,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>572155</v>
+        <v>572167</v>
       </c>
       <c r="R68" t="n">
-        <v>7078337</v>
+        <v>7078321</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7949,7 +7944,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7959,7 +7954,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7989,7 +7989,7 @@
         <v>128968892</v>
       </c>
       <c r="B69" t="n">
-        <v>96194</v>
+        <v>96195</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8291,45 +8291,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129337812</v>
+        <v>129341362</v>
       </c>
       <c r="B72" t="n">
-        <v>91713</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>571918</v>
+        <v>571975</v>
       </c>
       <c r="R72" t="n">
-        <v>7078355</v>
+        <v>7078298</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8362,6 +8367,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8388,50 +8398,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129341362</v>
+        <v>129337812</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>91713</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>571975</v>
+        <v>571918</v>
       </c>
       <c r="R73" t="n">
-        <v>7078298</v>
+        <v>7078355</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8464,11 +8469,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -4573,10 +4573,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128964493</v>
+        <v>128964288</v>
       </c>
       <c r="B37" t="n">
-        <v>79660</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4584,34 +4584,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572133</v>
+        <v>572121</v>
       </c>
       <c r="R37" t="n">
-        <v>7078367</v>
+        <v>7078371</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4643,7 +4648,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4653,7 +4658,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4680,10 +4690,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128964288</v>
+        <v>128964493</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>79662</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4691,39 +4701,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572121</v>
+        <v>572133</v>
       </c>
       <c r="R38" t="n">
-        <v>7078371</v>
+        <v>7078367</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4755,7 +4760,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4765,12 +4770,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4800,7 +4800,7 @@
         <v>128964085</v>
       </c>
       <c r="B39" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>128968891</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>128964559</v>
       </c>
       <c r="B41" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5108,48 +5108,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128963682</v>
+        <v>128968879</v>
       </c>
       <c r="B42" t="n">
-        <v>92826</v>
+        <v>57887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571916</v>
+        <v>571970</v>
       </c>
       <c r="R42" t="n">
-        <v>7078360</v>
+        <v>7078312</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5176,19 +5176,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5203,60 +5193,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128968879</v>
+        <v>128963682</v>
       </c>
       <c r="B43" t="n">
-        <v>57887</v>
+        <v>92829</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>571970</v>
+        <v>571916</v>
       </c>
       <c r="R43" t="n">
-        <v>7078312</v>
+        <v>7078360</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5283,9 +5273,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5300,12 +5300,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5315,7 +5315,7 @@
         <v>128964321</v>
       </c>
       <c r="B44" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>128968893</v>
       </c>
       <c r="B45" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>128963835</v>
       </c>
       <c r="B46" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>128968897</v>
       </c>
       <c r="B47" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>128963734</v>
       </c>
       <c r="B48" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>128964635</v>
       </c>
       <c r="B49" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>128963876</v>
       </c>
       <c r="B50" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>128967046</v>
       </c>
       <c r="B51" t="n">
-        <v>92838</v>
+        <v>92841</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>128968900</v>
       </c>
       <c r="B52" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>128968899</v>
       </c>
       <c r="B53" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6464,10 +6464,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128964488</v>
+        <v>128964016</v>
       </c>
       <c r="B55" t="n">
-        <v>78798</v>
+        <v>92851</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6475,21 +6475,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>5448</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572134</v>
+        <v>572005</v>
       </c>
       <c r="R55" t="n">
-        <v>7078366</v>
+        <v>7078331</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6571,10 +6571,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128964016</v>
+        <v>128963789</v>
       </c>
       <c r="B56" t="n">
-        <v>92848</v>
+        <v>92819</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6582,34 +6582,43 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572005</v>
+        <v>571944</v>
       </c>
       <c r="R56" t="n">
-        <v>7078331</v>
+        <v>7078381</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6641,7 +6650,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6651,7 +6660,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6678,10 +6687,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128963789</v>
+        <v>128964488</v>
       </c>
       <c r="B57" t="n">
-        <v>92816</v>
+        <v>78800</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6689,43 +6698,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>571944</v>
+        <v>572134</v>
       </c>
       <c r="R57" t="n">
-        <v>7078381</v>
+        <v>7078366</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6794,50 +6794,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128964140</v>
+        <v>128967070</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>92825</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572050</v>
+        <v>571779</v>
       </c>
       <c r="R58" t="n">
-        <v>7078406</v>
+        <v>7078375</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6869,7 +6864,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6879,12 +6874,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6911,10 +6901,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128963996</v>
+        <v>128968889</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6922,42 +6912,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572001</v>
+        <v>572173</v>
       </c>
       <c r="R59" t="n">
-        <v>7078333</v>
+        <v>7078310</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6984,24 +6969,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7016,57 +6991,62 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128967070</v>
+        <v>128964140</v>
       </c>
       <c r="B60" t="n">
-        <v>92822</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>571779</v>
+        <v>572050</v>
       </c>
       <c r="R60" t="n">
-        <v>7078375</v>
+        <v>7078406</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7098,7 +7078,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7108,7 +7088,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7135,10 +7120,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128968889</v>
+        <v>128963996</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7146,37 +7131,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572173</v>
+        <v>572001</v>
       </c>
       <c r="R61" t="n">
-        <v>7078310</v>
+        <v>7078333</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7203,14 +7193,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7225,12 +7225,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7240,7 +7240,7 @@
         <v>128968898</v>
       </c>
       <c r="B62" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>128964127</v>
       </c>
       <c r="B63" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>128964698</v>
       </c>
       <c r="B64" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7548,10 +7548,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128964587</v>
+        <v>128964634</v>
       </c>
       <c r="B65" t="n">
-        <v>90572</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7559,34 +7559,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572155</v>
+        <v>572167</v>
       </c>
       <c r="R65" t="n">
-        <v>7078337</v>
+        <v>7078321</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7618,7 +7623,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7628,7 +7633,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7655,32 +7665,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128964295</v>
+        <v>128964587</v>
       </c>
       <c r="B66" t="n">
-        <v>92822</v>
+        <v>90575</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7690,10 +7700,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572110</v>
+        <v>572155</v>
       </c>
       <c r="R66" t="n">
-        <v>7078382</v>
+        <v>7078337</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7725,7 +7735,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7735,7 +7745,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7750,44 +7760,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128964712</v>
+        <v>128964295</v>
       </c>
       <c r="B67" t="n">
-        <v>79041</v>
+        <v>92825</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7797,10 +7807,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572171</v>
+        <v>572110</v>
       </c>
       <c r="R67" t="n">
-        <v>7078312</v>
+        <v>7078382</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7832,7 +7842,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7842,7 +7852,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7869,10 +7879,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128964634</v>
+        <v>128964712</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7880,39 +7890,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>572167</v>
+        <v>572171</v>
       </c>
       <c r="R68" t="n">
-        <v>7078321</v>
+        <v>7078312</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7944,7 +7949,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7954,12 +7959,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7974,12 +7974,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7989,7 +7989,7 @@
         <v>128968892</v>
       </c>
       <c r="B69" t="n">
-        <v>96195</v>
+        <v>96199</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>129341563</v>
       </c>
       <c r="B70" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>129340276</v>
       </c>
       <c r="B71" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>129337812</v>
       </c>
       <c r="B73" t="n">
-        <v>91713</v>
+        <v>91716</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -5312,53 +5312,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128964321</v>
+        <v>128968893</v>
       </c>
       <c r="B44" t="n">
-        <v>78709</v>
+        <v>92825</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572123</v>
+        <v>571944</v>
       </c>
       <c r="R44" t="n">
-        <v>7078382</v>
+        <v>7078352</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5385,19 +5380,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5412,60 +5397,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128968893</v>
+        <v>128964321</v>
       </c>
       <c r="B45" t="n">
-        <v>92825</v>
+        <v>78709</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571944</v>
+        <v>572123</v>
       </c>
       <c r="R45" t="n">
-        <v>7078352</v>
+        <v>7078382</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5492,9 +5482,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5509,12 +5509,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6250,48 +6250,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128968899</v>
+        <v>128967185</v>
       </c>
       <c r="B53" t="n">
-        <v>92825</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572007</v>
+        <v>571833</v>
       </c>
       <c r="R53" t="n">
-        <v>7078343</v>
+        <v>7078283</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6318,9 +6323,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6335,65 +6355,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128967185</v>
+        <v>128968899</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>92825</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>571833</v>
+        <v>572007</v>
       </c>
       <c r="R54" t="n">
-        <v>7078283</v>
+        <v>7078343</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6420,24 +6435,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>17:27</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>17:27</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6452,12 +6452,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -4573,10 +4573,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128964288</v>
+        <v>128964493</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>79663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4584,39 +4584,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572121</v>
+        <v>572133</v>
       </c>
       <c r="R37" t="n">
-        <v>7078371</v>
+        <v>7078367</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4648,7 +4643,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4658,12 +4653,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4690,10 +4680,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128964493</v>
+        <v>128964288</v>
       </c>
       <c r="B38" t="n">
-        <v>79662</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4701,34 +4691,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572133</v>
+        <v>572121</v>
       </c>
       <c r="R38" t="n">
-        <v>7078367</v>
+        <v>7078371</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4760,7 +4755,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4770,7 +4765,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4800,7 +4800,7 @@
         <v>128964085</v>
       </c>
       <c r="B39" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>128968891</v>
       </c>
       <c r="B40" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>128964559</v>
       </c>
       <c r="B41" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>128963682</v>
       </c>
       <c r="B43" t="n">
-        <v>92829</v>
+        <v>92831</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5312,48 +5312,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128968893</v>
+        <v>128964321</v>
       </c>
       <c r="B44" t="n">
-        <v>92825</v>
+        <v>78710</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571944</v>
+        <v>572123</v>
       </c>
       <c r="R44" t="n">
-        <v>7078352</v>
+        <v>7078382</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5380,9 +5385,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5397,65 +5412,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128964321</v>
+        <v>128968893</v>
       </c>
       <c r="B45" t="n">
-        <v>78709</v>
+        <v>92827</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572123</v>
+        <v>571944</v>
       </c>
       <c r="R45" t="n">
-        <v>7078382</v>
+        <v>7078352</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5482,19 +5492,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5509,12 +5509,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5524,7 +5524,7 @@
         <v>128963835</v>
       </c>
       <c r="B46" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>128968897</v>
       </c>
       <c r="B47" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>128963734</v>
       </c>
       <c r="B48" t="n">
-        <v>92819</v>
+        <v>92821</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>128964635</v>
       </c>
       <c r="B49" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>128963876</v>
       </c>
       <c r="B50" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6046,48 +6046,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128967046</v>
+        <v>128968900</v>
       </c>
       <c r="B51" t="n">
-        <v>92841</v>
+        <v>92827</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>571822</v>
+        <v>571998</v>
       </c>
       <c r="R51" t="n">
-        <v>7078359</v>
+        <v>7078374</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6114,19 +6114,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>17:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6141,60 +6131,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128968900</v>
+        <v>128967046</v>
       </c>
       <c r="B52" t="n">
-        <v>92825</v>
+        <v>92843</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>571998</v>
+        <v>571822</v>
       </c>
       <c r="R52" t="n">
-        <v>7078374</v>
+        <v>7078359</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6221,9 +6211,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6238,65 +6238,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128967185</v>
+        <v>128968899</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>92827</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>571833</v>
+        <v>572007</v>
       </c>
       <c r="R53" t="n">
-        <v>7078283</v>
+        <v>7078343</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6323,24 +6318,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>17:27</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>17:27</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6355,60 +6335,65 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128968899</v>
+        <v>128967185</v>
       </c>
       <c r="B54" t="n">
-        <v>92825</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572007</v>
+        <v>571833</v>
       </c>
       <c r="R54" t="n">
-        <v>7078343</v>
+        <v>7078283</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6435,9 +6420,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6452,22 +6452,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128964016</v>
+        <v>128963789</v>
       </c>
       <c r="B55" t="n">
-        <v>92851</v>
+        <v>92821</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6475,34 +6475,43 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572005</v>
+        <v>571944</v>
       </c>
       <c r="R55" t="n">
-        <v>7078331</v>
+        <v>7078381</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6534,7 +6543,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6544,7 +6553,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6571,10 +6580,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128963789</v>
+        <v>128964488</v>
       </c>
       <c r="B56" t="n">
-        <v>92819</v>
+        <v>78801</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6582,43 +6591,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>571944</v>
+        <v>572134</v>
       </c>
       <c r="R56" t="n">
-        <v>7078381</v>
+        <v>7078366</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6687,10 +6687,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128964488</v>
+        <v>128964016</v>
       </c>
       <c r="B57" t="n">
-        <v>78800</v>
+        <v>92853</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6698,21 +6698,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>5448</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6722,10 +6722,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572134</v>
+        <v>572005</v>
       </c>
       <c r="R57" t="n">
-        <v>7078366</v>
+        <v>7078331</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6797,7 +6797,7 @@
         <v>128967070</v>
       </c>
       <c r="B58" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6901,10 +6901,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128968889</v>
+        <v>128963996</v>
       </c>
       <c r="B59" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6912,37 +6912,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572173</v>
+        <v>572001</v>
       </c>
       <c r="R59" t="n">
-        <v>7078310</v>
+        <v>7078333</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6969,14 +6974,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6991,12 +7006,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7120,10 +7135,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128963996</v>
+        <v>128968889</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7131,42 +7146,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572001</v>
+        <v>572173</v>
       </c>
       <c r="R61" t="n">
-        <v>7078333</v>
+        <v>7078310</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7193,24 +7203,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7225,12 +7225,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7240,7 +7240,7 @@
         <v>128968898</v>
       </c>
       <c r="B62" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>128964127</v>
       </c>
       <c r="B63" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>128964698</v>
       </c>
       <c r="B64" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7548,10 +7548,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128964634</v>
+        <v>128964587</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>90577</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7559,39 +7559,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572167</v>
+        <v>572155</v>
       </c>
       <c r="R65" t="n">
-        <v>7078321</v>
+        <v>7078337</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7623,7 +7618,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7633,12 +7628,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7665,32 +7655,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128964587</v>
+        <v>128964295</v>
       </c>
       <c r="B66" t="n">
-        <v>90575</v>
+        <v>92827</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7700,10 +7690,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572155</v>
+        <v>572110</v>
       </c>
       <c r="R66" t="n">
-        <v>7078337</v>
+        <v>7078382</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7735,7 +7725,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7745,7 +7735,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7760,57 +7750,62 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128964295</v>
+        <v>128964634</v>
       </c>
       <c r="B67" t="n">
-        <v>92825</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572110</v>
+        <v>572167</v>
       </c>
       <c r="R67" t="n">
-        <v>7078382</v>
+        <v>7078321</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7842,7 +7837,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7852,7 +7847,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7867,12 +7867,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7882,7 +7882,7 @@
         <v>128964712</v>
       </c>
       <c r="B68" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>128968892</v>
       </c>
       <c r="B69" t="n">
-        <v>96199</v>
+        <v>96201</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>129341563</v>
       </c>
       <c r="B70" t="n">
-        <v>90575</v>
+        <v>90577</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>129340276</v>
       </c>
       <c r="B71" t="n">
-        <v>91961</v>
+        <v>91963</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8291,50 +8291,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129341362</v>
+        <v>129337812</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>91718</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>571975</v>
+        <v>571918</v>
       </c>
       <c r="R72" t="n">
-        <v>7078298</v>
+        <v>7078355</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8367,11 +8362,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8398,45 +8388,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129337812</v>
+        <v>129341362</v>
       </c>
       <c r="B73" t="n">
-        <v>91716</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>571918</v>
+        <v>571975</v>
       </c>
       <c r="R73" t="n">
-        <v>7078355</v>
+        <v>7078298</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8469,6 +8464,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -4573,10 +4573,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128964493</v>
+        <v>128964288</v>
       </c>
       <c r="B37" t="n">
-        <v>79663</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4584,34 +4584,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572133</v>
+        <v>572121</v>
       </c>
       <c r="R37" t="n">
-        <v>7078367</v>
+        <v>7078371</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4643,7 +4648,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4653,7 +4658,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4680,10 +4690,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128964288</v>
+        <v>128964493</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>79663</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4691,39 +4701,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572121</v>
+        <v>572133</v>
       </c>
       <c r="R38" t="n">
-        <v>7078371</v>
+        <v>7078367</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4755,7 +4760,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4765,12 +4770,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4800,7 +4800,7 @@
         <v>128964085</v>
       </c>
       <c r="B39" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>128963682</v>
       </c>
       <c r="B43" t="n">
-        <v>92831</v>
+        <v>92835</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5312,53 +5312,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128964321</v>
+        <v>128968893</v>
       </c>
       <c r="B44" t="n">
-        <v>78710</v>
+        <v>92831</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572123</v>
+        <v>571944</v>
       </c>
       <c r="R44" t="n">
-        <v>7078382</v>
+        <v>7078352</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5385,19 +5380,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5412,60 +5397,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128968893</v>
+        <v>128964321</v>
       </c>
       <c r="B45" t="n">
-        <v>92827</v>
+        <v>78710</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571944</v>
+        <v>572123</v>
       </c>
       <c r="R45" t="n">
-        <v>7078352</v>
+        <v>7078382</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5492,9 +5482,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5509,12 +5509,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5524,7 +5524,7 @@
         <v>128963835</v>
       </c>
       <c r="B46" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>128968897</v>
       </c>
       <c r="B47" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>128963734</v>
       </c>
       <c r="B48" t="n">
-        <v>92821</v>
+        <v>92825</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>128964635</v>
       </c>
       <c r="B49" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>128963876</v>
       </c>
       <c r="B50" t="n">
-        <v>92839</v>
+        <v>92843</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>128968900</v>
       </c>
       <c r="B51" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>128967046</v>
       </c>
       <c r="B52" t="n">
-        <v>92843</v>
+        <v>92847</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>128968899</v>
       </c>
       <c r="B53" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>128963789</v>
       </c>
       <c r="B55" t="n">
-        <v>92821</v>
+        <v>92825</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6580,10 +6580,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128964488</v>
+        <v>128964016</v>
       </c>
       <c r="B56" t="n">
-        <v>78801</v>
+        <v>92857</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>5448</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572134</v>
+        <v>572005</v>
       </c>
       <c r="R56" t="n">
-        <v>7078366</v>
+        <v>7078331</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6687,10 +6687,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128964016</v>
+        <v>128964488</v>
       </c>
       <c r="B57" t="n">
-        <v>92853</v>
+        <v>78801</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6698,21 +6698,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5448</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6722,10 +6722,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572005</v>
+        <v>572134</v>
       </c>
       <c r="R57" t="n">
-        <v>7078331</v>
+        <v>7078366</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6794,48 +6794,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128967070</v>
+        <v>128968889</v>
       </c>
       <c r="B58" t="n">
-        <v>92827</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>571779</v>
+        <v>572173</v>
       </c>
       <c r="R58" t="n">
-        <v>7078375</v>
+        <v>7078310</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6862,19 +6862,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>17:24</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6889,19 +6884,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128963996</v>
+        <v>128964140</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -6941,10 +6936,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572001</v>
+        <v>572050</v>
       </c>
       <c r="R59" t="n">
-        <v>7078333</v>
+        <v>7078406</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6976,7 +6971,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6986,7 +6981,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -7006,19 +7001,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128964140</v>
+        <v>128963996</v>
       </c>
       <c r="B60" t="n">
         <v>57727</v>
@@ -7058,10 +7053,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572050</v>
+        <v>572001</v>
       </c>
       <c r="R60" t="n">
-        <v>7078406</v>
+        <v>7078333</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7093,7 +7088,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7103,7 +7098,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7123,60 +7118,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128968889</v>
+        <v>128967070</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>92831</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572173</v>
+        <v>571779</v>
       </c>
       <c r="R61" t="n">
-        <v>7078310</v>
+        <v>7078375</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7203,14 +7198,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7225,12 +7225,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7240,7 +7240,7 @@
         <v>128968898</v>
       </c>
       <c r="B62" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>128964127</v>
       </c>
       <c r="B63" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>128964698</v>
       </c>
       <c r="B64" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7548,10 +7548,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128964587</v>
+        <v>128964634</v>
       </c>
       <c r="B65" t="n">
-        <v>90577</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7559,34 +7559,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572155</v>
+        <v>572167</v>
       </c>
       <c r="R65" t="n">
-        <v>7078337</v>
+        <v>7078321</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7618,7 +7623,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7628,7 +7633,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7655,32 +7665,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128964295</v>
+        <v>128964587</v>
       </c>
       <c r="B66" t="n">
-        <v>92827</v>
+        <v>90581</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7690,10 +7700,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572110</v>
+        <v>572155</v>
       </c>
       <c r="R66" t="n">
-        <v>7078382</v>
+        <v>7078337</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7725,7 +7735,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7735,7 +7745,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7750,22 +7760,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128964634</v>
+        <v>128964712</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7773,39 +7783,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572167</v>
+        <v>572171</v>
       </c>
       <c r="R67" t="n">
-        <v>7078321</v>
+        <v>7078312</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7837,7 +7842,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7847,12 +7852,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7867,44 +7867,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128964712</v>
+        <v>128964295</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>92831</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7914,10 +7914,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>572171</v>
+        <v>572110</v>
       </c>
       <c r="R68" t="n">
-        <v>7078312</v>
+        <v>7078382</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7989,7 +7989,7 @@
         <v>128968892</v>
       </c>
       <c r="B69" t="n">
-        <v>96201</v>
+        <v>96205</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>129341563</v>
       </c>
       <c r="B70" t="n">
-        <v>90577</v>
+        <v>90581</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>129340276</v>
       </c>
       <c r="B71" t="n">
-        <v>91963</v>
+        <v>91967</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>129337812</v>
       </c>
       <c r="B72" t="n">
-        <v>91718</v>
+        <v>91722</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -4800,7 +4800,7 @@
         <v>128964085</v>
       </c>
       <c r="B39" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>128963682</v>
       </c>
       <c r="B43" t="n">
-        <v>92835</v>
+        <v>92836</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>128968893</v>
       </c>
       <c r="B44" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>128963835</v>
       </c>
       <c r="B46" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>128968897</v>
       </c>
       <c r="B47" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>128963734</v>
       </c>
       <c r="B48" t="n">
-        <v>92825</v>
+        <v>92826</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>128964635</v>
       </c>
       <c r="B49" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>128963876</v>
       </c>
       <c r="B50" t="n">
-        <v>92843</v>
+        <v>92844</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>128968900</v>
       </c>
       <c r="B51" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>128967046</v>
       </c>
       <c r="B52" t="n">
-        <v>92847</v>
+        <v>92848</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>128968899</v>
       </c>
       <c r="B53" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>128963789</v>
       </c>
       <c r="B55" t="n">
-        <v>92825</v>
+        <v>92826</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>128964016</v>
       </c>
       <c r="B56" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6794,48 +6794,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128968889</v>
+        <v>128967070</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572173</v>
+        <v>571779</v>
       </c>
       <c r="R58" t="n">
-        <v>7078310</v>
+        <v>7078375</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6862,14 +6862,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6884,12 +6889,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7130,48 +7135,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128967070</v>
+        <v>128968889</v>
       </c>
       <c r="B61" t="n">
-        <v>92831</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>571779</v>
+        <v>572173</v>
       </c>
       <c r="R61" t="n">
-        <v>7078375</v>
+        <v>7078310</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7198,19 +7203,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>17:24</t>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7225,12 +7225,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7240,7 +7240,7 @@
         <v>128968898</v>
       </c>
       <c r="B62" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>128964127</v>
       </c>
       <c r="B63" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>128964698</v>
       </c>
       <c r="B64" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7548,50 +7548,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128964634</v>
+        <v>128964295</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>92832</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572167</v>
+        <v>572110</v>
       </c>
       <c r="R65" t="n">
-        <v>7078321</v>
+        <v>7078382</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7623,7 +7618,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7633,12 +7628,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7653,22 +7643,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128964587</v>
+        <v>128964634</v>
       </c>
       <c r="B66" t="n">
-        <v>90581</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7676,34 +7666,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572155</v>
+        <v>572167</v>
       </c>
       <c r="R66" t="n">
-        <v>7078337</v>
+        <v>7078321</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7735,7 +7730,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7745,7 +7740,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7879,32 +7879,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128964295</v>
+        <v>128964587</v>
       </c>
       <c r="B68" t="n">
-        <v>92831</v>
+        <v>90582</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7914,10 +7914,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>572110</v>
+        <v>572155</v>
       </c>
       <c r="R68" t="n">
-        <v>7078382</v>
+        <v>7078337</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7974,12 +7974,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7989,7 +7989,7 @@
         <v>128968892</v>
       </c>
       <c r="B69" t="n">
-        <v>96205</v>
+        <v>96213</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>129341563</v>
       </c>
       <c r="B70" t="n">
-        <v>90581</v>
+        <v>90582</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>129340276</v>
       </c>
       <c r="B71" t="n">
-        <v>91967</v>
+        <v>91968</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>129337812</v>
       </c>
       <c r="B72" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4573,10 +4573,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128964288</v>
+        <v>128964493</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>79663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4584,39 +4584,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572121</v>
+        <v>572133</v>
       </c>
       <c r="R37" t="n">
-        <v>7078371</v>
+        <v>7078367</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4648,7 +4643,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4658,12 +4653,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4690,10 +4680,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128964493</v>
+        <v>128964288</v>
       </c>
       <c r="B38" t="n">
-        <v>79663</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4701,34 +4691,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572133</v>
+        <v>572121</v>
       </c>
       <c r="R38" t="n">
-        <v>7078367</v>
+        <v>7078371</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4760,7 +4755,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4770,7 +4765,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5312,48 +5312,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128968893</v>
+        <v>128964321</v>
       </c>
       <c r="B44" t="n">
-        <v>92832</v>
+        <v>78710</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571944</v>
+        <v>572123</v>
       </c>
       <c r="R44" t="n">
-        <v>7078352</v>
+        <v>7078382</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5380,9 +5385,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5397,65 +5412,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128964321</v>
+        <v>128968893</v>
       </c>
       <c r="B45" t="n">
-        <v>78710</v>
+        <v>92832</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572123</v>
+        <v>571944</v>
       </c>
       <c r="R45" t="n">
-        <v>7078382</v>
+        <v>7078352</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5482,19 +5492,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5509,12 +5509,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6046,48 +6046,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128968900</v>
+        <v>128967046</v>
       </c>
       <c r="B51" t="n">
-        <v>92832</v>
+        <v>92848</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>571998</v>
+        <v>571822</v>
       </c>
       <c r="R51" t="n">
-        <v>7078374</v>
+        <v>7078359</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6114,9 +6114,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6131,60 +6141,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128967046</v>
+        <v>128968900</v>
       </c>
       <c r="B52" t="n">
-        <v>92848</v>
+        <v>92832</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>571822</v>
+        <v>571998</v>
       </c>
       <c r="R52" t="n">
-        <v>7078359</v>
+        <v>7078374</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6211,19 +6221,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>17:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6238,60 +6238,65 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128968899</v>
+        <v>128967185</v>
       </c>
       <c r="B53" t="n">
-        <v>92832</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572007</v>
+        <v>571833</v>
       </c>
       <c r="R53" t="n">
-        <v>7078343</v>
+        <v>7078283</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6318,9 +6323,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6335,65 +6355,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128967185</v>
+        <v>128968899</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>92832</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>571833</v>
+        <v>572007</v>
       </c>
       <c r="R54" t="n">
-        <v>7078283</v>
+        <v>7078343</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6420,24 +6435,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>17:27</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>17:27</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6452,22 +6452,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128963789</v>
+        <v>128964016</v>
       </c>
       <c r="B55" t="n">
-        <v>92826</v>
+        <v>92858</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6475,43 +6475,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>571944</v>
+        <v>572005</v>
       </c>
       <c r="R55" t="n">
-        <v>7078381</v>
+        <v>7078331</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6543,7 +6534,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6553,7 +6544,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6580,10 +6571,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128964016</v>
+        <v>128963789</v>
       </c>
       <c r="B56" t="n">
-        <v>92858</v>
+        <v>92826</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6591,34 +6582,43 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572005</v>
+        <v>571944</v>
       </c>
       <c r="R56" t="n">
-        <v>7078331</v>
+        <v>7078381</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7548,32 +7548,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128964295</v>
+        <v>128964712</v>
       </c>
       <c r="B65" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7583,10 +7583,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572110</v>
+        <v>572171</v>
       </c>
       <c r="R65" t="n">
-        <v>7078382</v>
+        <v>7078312</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7655,10 +7655,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128964634</v>
+        <v>128964587</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>90582</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,39 +7666,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572167</v>
+        <v>572155</v>
       </c>
       <c r="R66" t="n">
-        <v>7078321</v>
+        <v>7078337</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7730,7 +7725,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7740,12 +7735,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7772,32 +7762,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128964712</v>
+        <v>128964295</v>
       </c>
       <c r="B67" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7807,10 +7797,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572171</v>
+        <v>572110</v>
       </c>
       <c r="R67" t="n">
-        <v>7078312</v>
+        <v>7078382</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7842,7 +7832,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7852,7 +7842,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7879,10 +7869,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128964587</v>
+        <v>128964634</v>
       </c>
       <c r="B68" t="n">
-        <v>90582</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7890,34 +7880,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>572155</v>
+        <v>572167</v>
       </c>
       <c r="R68" t="n">
-        <v>7078337</v>
+        <v>7078321</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7949,7 +7944,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7959,7 +7954,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8609,6 +8609,113 @@
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128963699</v>
+      </c>
+      <c r="B75" t="n">
+        <v>91723</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>571919</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7078362</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8716,6 +8716,113 @@
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128964674</v>
+      </c>
+      <c r="B76" t="n">
+        <v>96213</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>572162</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7078308</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -8086,7 +8086,7 @@
         <v>129341563</v>
       </c>
       <c r="B70" t="n">
-        <v>90582</v>
+        <v>90585</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>129340276</v>
       </c>
       <c r="B71" t="n">
-        <v>91968</v>
+        <v>91971</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>129337812</v>
       </c>
       <c r="B72" t="n">
-        <v>91723</v>
+        <v>91726</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>128963699</v>
       </c>
       <c r="B75" t="n">
-        <v>91723</v>
+        <v>91726</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>128964674</v>
       </c>
       <c r="B76" t="n">
-        <v>96213</v>
+        <v>96216</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -8291,45 +8291,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129337812</v>
+        <v>129341362</v>
       </c>
       <c r="B72" t="n">
-        <v>91726</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>571918</v>
+        <v>571975</v>
       </c>
       <c r="R72" t="n">
-        <v>7078355</v>
+        <v>7078298</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8362,6 +8367,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8388,50 +8398,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129341362</v>
+        <v>129337812</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>91726</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>571975</v>
+        <v>571918</v>
       </c>
       <c r="R73" t="n">
-        <v>7078298</v>
+        <v>7078355</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8464,11 +8469,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -8291,50 +8291,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129341362</v>
+        <v>129337812</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>91726</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>571975</v>
+        <v>571918</v>
       </c>
       <c r="R72" t="n">
-        <v>7078298</v>
+        <v>7078355</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8367,11 +8362,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8398,45 +8388,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129337812</v>
+        <v>129341362</v>
       </c>
       <c r="B73" t="n">
-        <v>91726</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>571918</v>
+        <v>571975</v>
       </c>
       <c r="R73" t="n">
-        <v>7078355</v>
+        <v>7078298</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8469,6 +8464,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -8086,7 +8086,7 @@
         <v>129341563</v>
       </c>
       <c r="B70" t="n">
-        <v>90585</v>
+        <v>90613</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>129340276</v>
       </c>
       <c r="B71" t="n">
-        <v>91971</v>
+        <v>91999</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8291,45 +8291,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129337812</v>
+        <v>129341362</v>
       </c>
       <c r="B72" t="n">
-        <v>91726</v>
+        <v>57730</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>571918</v>
+        <v>571975</v>
       </c>
       <c r="R72" t="n">
-        <v>7078355</v>
+        <v>7078298</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8362,6 +8367,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8388,50 +8398,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129341362</v>
+        <v>129337812</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>91754</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>571975</v>
+        <v>571918</v>
       </c>
       <c r="R73" t="n">
-        <v>7078298</v>
+        <v>7078355</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8464,11 +8469,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8498,7 +8498,7 @@
         <v>129403423</v>
       </c>
       <c r="B74" t="n">
-        <v>57831</v>
+        <v>57834</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>128963699</v>
       </c>
       <c r="B75" t="n">
-        <v>91726</v>
+        <v>91754</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>128964674</v>
       </c>
       <c r="B76" t="n">
-        <v>96216</v>
+        <v>96245</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -8291,50 +8291,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129341362</v>
+        <v>129337812</v>
       </c>
       <c r="B72" t="n">
-        <v>57730</v>
+        <v>91754</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>571975</v>
+        <v>571918</v>
       </c>
       <c r="R72" t="n">
-        <v>7078298</v>
+        <v>7078355</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8367,11 +8362,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8398,45 +8388,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129337812</v>
+        <v>129341362</v>
       </c>
       <c r="B73" t="n">
-        <v>91754</v>
+        <v>57730</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>571918</v>
+        <v>571975</v>
       </c>
       <c r="R73" t="n">
-        <v>7078355</v>
+        <v>7078298</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8469,6 +8464,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -8086,7 +8086,7 @@
         <v>129341563</v>
       </c>
       <c r="B70" t="n">
-        <v>90613</v>
+        <v>90619</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>129340276</v>
       </c>
       <c r="B71" t="n">
-        <v>91999</v>
+        <v>92005</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>129337812</v>
       </c>
       <c r="B72" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>129341362</v>
       </c>
       <c r="B73" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>129403423</v>
       </c>
       <c r="B74" t="n">
-        <v>57834</v>
+        <v>57839</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>128963699</v>
       </c>
       <c r="B75" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>128964674</v>
       </c>
       <c r="B76" t="n">
-        <v>96245</v>
+        <v>96257</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -8086,7 +8086,7 @@
         <v>129341563</v>
       </c>
       <c r="B70" t="n">
-        <v>90619</v>
+        <v>90620</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>129340276</v>
       </c>
       <c r="B71" t="n">
-        <v>92005</v>
+        <v>92006</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>129337812</v>
       </c>
       <c r="B72" t="n">
-        <v>91760</v>
+        <v>91761</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>129341362</v>
       </c>
       <c r="B73" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>129403423</v>
       </c>
       <c r="B74" t="n">
-        <v>57839</v>
+        <v>57840</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>128963699</v>
       </c>
       <c r="B75" t="n">
-        <v>91760</v>
+        <v>91761</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>128964674</v>
       </c>
       <c r="B76" t="n">
-        <v>96257</v>
+        <v>96258</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -8086,7 +8086,7 @@
         <v>129341563</v>
       </c>
       <c r="B70" t="n">
-        <v>90620</v>
+        <v>90625</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>129340276</v>
       </c>
       <c r="B71" t="n">
-        <v>92006</v>
+        <v>92011</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>129337812</v>
       </c>
       <c r="B72" t="n">
-        <v>91761</v>
+        <v>91766</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>128963699</v>
       </c>
       <c r="B75" t="n">
-        <v>91761</v>
+        <v>91766</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>128964674</v>
       </c>
       <c r="B76" t="n">
-        <v>96258</v>
+        <v>96263</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -8614,7 +8614,7 @@
         <v>128963699</v>
       </c>
       <c r="B75" t="n">
-        <v>91766</v>
+        <v>91770</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>128964674</v>
       </c>
       <c r="B76" t="n">
-        <v>96263</v>
+        <v>96267</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -8614,7 +8614,7 @@
         <v>128963699</v>
       </c>
       <c r="B75" t="n">
-        <v>91770</v>
+        <v>91772</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>128964674</v>
       </c>
       <c r="B76" t="n">
-        <v>96267</v>
+        <v>96269</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -8721,7 +8721,7 @@
         <v>128964674</v>
       </c>
       <c r="B76" t="n">
-        <v>96269</v>
+        <v>96279</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -8614,7 +8614,7 @@
         <v>128963699</v>
       </c>
       <c r="B75" t="n">
-        <v>91772</v>
+        <v>91775</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>128964674</v>
       </c>
       <c r="B76" t="n">
-        <v>96279</v>
+        <v>96283</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY106"/>
+  <dimension ref="A1:AZ106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964321</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964559</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118263398</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128963699</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129337812</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964587</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129341563</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1503,6 +1543,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128967046</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1610,6 +1655,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964674</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1707,6 +1757,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968892</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1808,6 +1863,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97375762</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1915,6 +1975,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128963734</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2031,6 +2096,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128963789</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2138,6 +2208,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127836170</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2245,6 +2320,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127836515</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2352,6 +2432,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127836645</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2459,6 +2544,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127836771</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2566,6 +2656,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127836852</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2673,6 +2768,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127836856</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2780,6 +2880,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837089</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2887,6 +2992,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837312</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2994,6 +3104,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837382</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3101,6 +3216,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837562</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3208,6 +3328,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127839665</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3315,6 +3440,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128963835</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3422,6 +3552,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964085</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3529,6 +3664,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964127</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3636,6 +3776,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964295</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3743,6 +3888,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964518</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3850,6 +4000,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964635</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3957,6 +4112,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964698</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4064,6 +4224,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128967070</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4161,6 +4326,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968893</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4258,6 +4428,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968897</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4355,6 +4530,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968898</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4452,6 +4632,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968899</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4549,6 +4734,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968900</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4656,6 +4846,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128963682</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4763,6 +4958,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128963712</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4870,6 +5070,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128963876</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4977,6 +5182,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127838783</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5084,6 +5294,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964016</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5185,6 +5400,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97375764</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5292,6 +5512,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127836491</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5399,6 +5624,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837544</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5506,6 +5736,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837620</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5613,6 +5848,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837817</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5720,6 +5960,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964712</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5822,6 +6067,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968889</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5919,6 +6169,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968891</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6026,6 +6281,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837626</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6133,6 +6393,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964488</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6240,6 +6505,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964562</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6347,6 +6617,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964737</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6454,6 +6729,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964493</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6571,6 +6851,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127835362</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6688,6 +6973,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127835378</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6805,6 +7095,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127835846</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6922,6 +7217,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127836182</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7039,6 +7339,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127836801</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7156,6 +7461,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837292</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7273,6 +7583,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837661</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7390,6 +7705,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837719</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7507,6 +7827,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837781</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7624,6 +7949,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837867</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7741,6 +8071,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837928</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7858,6 +8193,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837929</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7975,6 +8315,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837949</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8092,6 +8437,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837969</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8209,6 +8559,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837975</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8326,6 +8681,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127838069</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8443,6 +8803,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127838072</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8560,6 +8925,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127838220</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8677,6 +9047,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127838273</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8794,6 +9169,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127838341</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8911,6 +9291,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127838414</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9028,6 +9413,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127838705</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9145,6 +9535,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127839277</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9262,6 +9657,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127839604</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9379,6 +9779,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127839625</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9496,6 +9901,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128963996</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9613,6 +10023,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964140</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9730,6 +10145,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964288</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9847,6 +10267,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964634</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9964,6 +10389,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128967185</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10071,6 +10501,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129341362</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10168,6 +10603,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118263401</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10284,6 +10724,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837406</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10381,6 +10826,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968879</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10497,6 +10947,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129403423</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10594,6 +11049,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118263409</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10691,6 +11151,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118263411</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10807,6 +11272,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127839160</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10904,6 +11374,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968885</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11001,6 +11476,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118263404</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11108,6 +11588,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127836444</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11215,6 +11700,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127836986</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11322,6 +11812,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127837171</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11429,6 +11924,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127838430</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11536,6 +12036,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127839595</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11643,6 +12148,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128964377</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11740,6 +12250,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339963</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11847,6 +12362,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129341318</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11944,6 +12464,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129341334</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12060,8 +12585,120 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129340276</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>128964674</v>
       </c>
       <c r="B10" t="n">
-        <v>96601</v>
+        <v>96772</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128968892</v>
       </c>
       <c r="B11" t="n">
-        <v>96601</v>
+        <v>96772</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>128964674</v>
       </c>
       <c r="B10" t="n">
-        <v>96772</v>
+        <v>96773</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128968892</v>
       </c>
       <c r="B11" t="n">
-        <v>96772</v>
+        <v>96773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>128964674</v>
       </c>
       <c r="B10" t="n">
-        <v>96773</v>
+        <v>96774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128968892</v>
       </c>
       <c r="B11" t="n">
-        <v>96773</v>
+        <v>96774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>128964674</v>
       </c>
       <c r="B10" t="n">
-        <v>96774</v>
+        <v>96780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128968892</v>
       </c>
       <c r="B11" t="n">
-        <v>96774</v>
+        <v>96780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>128964674</v>
       </c>
       <c r="B10" t="n">
-        <v>96780</v>
+        <v>96781</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128968892</v>
       </c>
       <c r="B11" t="n">
-        <v>96780</v>
+        <v>96781</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>128964674</v>
       </c>
       <c r="B10" t="n">
-        <v>96781</v>
+        <v>96792</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128968892</v>
       </c>
       <c r="B11" t="n">
-        <v>96781</v>
+        <v>96792</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>128964674</v>
       </c>
       <c r="B10" t="n">
-        <v>96792</v>
+        <v>96805</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128968892</v>
       </c>
       <c r="B11" t="n">
-        <v>96792</v>
+        <v>96805</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>128964674</v>
       </c>
       <c r="B10" t="n">
-        <v>96805</v>
+        <v>96806</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128968892</v>
       </c>
       <c r="B11" t="n">
-        <v>96805</v>
+        <v>96806</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>128964674</v>
       </c>
       <c r="B10" t="n">
-        <v>96806</v>
+        <v>96819</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128968892</v>
       </c>
       <c r="B11" t="n">
-        <v>96806</v>
+        <v>96819</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>128964674</v>
       </c>
       <c r="B10" t="n">
-        <v>96819</v>
+        <v>96820</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128968892</v>
       </c>
       <c r="B11" t="n">
-        <v>96819</v>
+        <v>96820</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
